--- a/Deliverables/HUB/BOM/Client_BOM_Ezlo_Voice_AssistantHUB.xlsx
+++ b/Deliverables/HUB/BOM/Client_BOM_Ezlo_Voice_AssistantHUB.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverables\HUB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F93E35-CC84-4AD2-B3F0-0EBEB056A1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C9F151-1C91-4840-BA60-583F120B86A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5715" yWindow="3975" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="515">
   <si>
     <t>Component list</t>
   </si>
@@ -1587,7 +1586,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1742,14 +1741,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2021,7 +2012,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2169,15 +2160,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2214,6 +2196,21 @@
     <xf numFmtId="166" fontId="14" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -2222,25 +2219,14 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2614,13 +2600,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
     </row>
     <row r="2" spans="1:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2664,7 +2650,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="57"/>
+      <c r="P3" s="71"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2686,7 +2672,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="58"/>
+      <c r="P4" s="72"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2708,7 +2694,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="58"/>
+      <c r="P5" s="72"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2726,7 +2712,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="58"/>
+      <c r="P6" s="72"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2744,7 +2730,7 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="58"/>
+      <c r="P7" s="72"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2762,7 +2748,7 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="58"/>
+      <c r="P8" s="72"/>
     </row>
     <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2808,7 +2794,7 @@
       <c r="O9" s="29" t="s">
         <v>508</v>
       </c>
-      <c r="P9" s="59" t="s">
+      <c r="P9" s="56" t="s">
         <v>465</v>
       </c>
     </row>
@@ -2818,7 +2804,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="57" t="s">
         <v>466</v>
       </c>
       <c r="D10" s="36" t="s">
@@ -2848,13 +2834,13 @@
       <c r="L10" s="36">
         <v>12</v>
       </c>
-      <c r="M10" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N10" s="80">
+      <c r="M10" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N10" s="69">
         <v>0.21779999999999999</v>
       </c>
-      <c r="O10" s="66">
+      <c r="O10" s="63">
         <f>N10*L10</f>
         <v>2.6135999999999999</v>
       </c>
@@ -2866,7 +2852,7 @@
         <f t="shared" ref="B11:B119" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="58" t="s">
         <v>466</v>
       </c>
       <c r="D11" s="38" t="s">
@@ -2896,13 +2882,13 @@
       <c r="L11" s="38">
         <v>15</v>
       </c>
-      <c r="M11" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N11" s="68">
+      <c r="M11" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N11" s="65">
         <v>0.20350000000000001</v>
       </c>
-      <c r="O11" s="68">
+      <c r="O11" s="65">
         <f t="shared" ref="O11:O74" si="1">N11*L11</f>
         <v>3.0525000000000002</v>
       </c>
@@ -2914,7 +2900,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D12" s="36" t="s">
@@ -2944,13 +2930,13 @@
       <c r="L12" s="36">
         <v>100</v>
       </c>
-      <c r="M12" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N12" s="66">
+      <c r="M12" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N12" s="63">
         <v>0.10210000000000001</v>
       </c>
-      <c r="O12" s="66">
+      <c r="O12" s="63">
         <f t="shared" si="1"/>
         <v>10.210000000000001</v>
       </c>
@@ -2962,7 +2948,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D13" s="38" t="s">
@@ -2992,13 +2978,13 @@
       <c r="L13" s="38">
         <v>100</v>
       </c>
-      <c r="M13" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N13" s="68">
+      <c r="M13" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N13" s="65">
         <v>0.10300000000000001</v>
       </c>
-      <c r="O13" s="68">
+      <c r="O13" s="65">
         <f t="shared" si="1"/>
         <v>10.3</v>
       </c>
@@ -3010,7 +2996,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D14" s="36" t="s">
@@ -3040,13 +3026,13 @@
       <c r="L14" s="36">
         <v>80</v>
       </c>
-      <c r="M14" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N14" s="66">
+      <c r="M14" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N14" s="63">
         <v>0.11810000000000001</v>
       </c>
-      <c r="O14" s="66">
+      <c r="O14" s="63">
         <f t="shared" si="1"/>
         <v>9.4480000000000004</v>
       </c>
@@ -3058,7 +3044,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D15" s="38" t="s">
@@ -3088,13 +3074,13 @@
       <c r="L15" s="38">
         <v>1300</v>
       </c>
-      <c r="M15" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N15" s="68">
+      <c r="M15" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N15" s="65">
         <v>0.1009</v>
       </c>
-      <c r="O15" s="68">
+      <c r="O15" s="65">
         <f t="shared" si="1"/>
         <v>131.17000000000002</v>
       </c>
@@ -3106,7 +3092,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D16" s="36" t="s">
@@ -3118,7 +3104,7 @@
       <c r="F16" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="59" t="s">
         <v>286</v>
       </c>
       <c r="H16" s="36" t="s">
@@ -3136,13 +3122,13 @@
       <c r="L16" s="36">
         <v>180</v>
       </c>
-      <c r="M16" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N16" s="66">
+      <c r="M16" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N16" s="63">
         <v>0.11420000000000001</v>
       </c>
-      <c r="O16" s="66">
+      <c r="O16" s="63">
         <f t="shared" si="1"/>
         <v>20.556000000000001</v>
       </c>
@@ -3154,7 +3140,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D17" s="38" t="s">
@@ -3184,13 +3170,13 @@
       <c r="L17" s="38">
         <v>280</v>
       </c>
-      <c r="M17" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N17" s="68">
+      <c r="M17" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N17" s="65">
         <v>0.11360000000000001</v>
       </c>
-      <c r="O17" s="68">
+      <c r="O17" s="65">
         <f t="shared" si="1"/>
         <v>31.808000000000003</v>
       </c>
@@ -3202,7 +3188,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D18" s="36" t="s">
@@ -3232,13 +3218,13 @@
       <c r="L18" s="36">
         <v>300</v>
       </c>
-      <c r="M18" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N18" s="66">
+      <c r="M18" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N18" s="63">
         <v>0.1052</v>
       </c>
-      <c r="O18" s="66">
+      <c r="O18" s="63">
         <f t="shared" si="1"/>
         <v>31.560000000000002</v>
       </c>
@@ -3250,7 +3236,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D19" s="38" t="s">
@@ -3280,13 +3266,13 @@
       <c r="L19" s="38">
         <v>100</v>
       </c>
-      <c r="M19" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N19" s="68">
+      <c r="M19" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N19" s="65">
         <v>0.10310000000000001</v>
       </c>
-      <c r="O19" s="68">
+      <c r="O19" s="65">
         <f t="shared" si="1"/>
         <v>10.31</v>
       </c>
@@ -3298,7 +3284,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D20" s="36" t="s">
@@ -3328,13 +3314,13 @@
       <c r="L20" s="36">
         <v>50</v>
       </c>
-      <c r="M20" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N20" s="66">
+      <c r="M20" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N20" s="63">
         <v>0.10750000000000001</v>
       </c>
-      <c r="O20" s="66">
+      <c r="O20" s="63">
         <f t="shared" si="1"/>
         <v>5.3750000000000009</v>
       </c>
@@ -3346,7 +3332,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D21" s="38" t="s">
@@ -3376,13 +3362,13 @@
       <c r="L21" s="38">
         <v>100</v>
       </c>
-      <c r="M21" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N21" s="68">
+      <c r="M21" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N21" s="65">
         <v>0.10290000000000001</v>
       </c>
-      <c r="O21" s="68">
+      <c r="O21" s="65">
         <f t="shared" si="1"/>
         <v>10.290000000000001</v>
       </c>
@@ -3394,7 +3380,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D22" s="36" t="s">
@@ -3424,13 +3410,13 @@
       <c r="L22" s="36">
         <v>50</v>
       </c>
-      <c r="M22" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N22" s="66">
+      <c r="M22" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N22" s="63">
         <v>0.11330000000000001</v>
       </c>
-      <c r="O22" s="66">
+      <c r="O22" s="63">
         <f t="shared" si="1"/>
         <v>5.6650000000000009</v>
       </c>
@@ -3442,7 +3428,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D23" s="38" t="s">
@@ -3472,13 +3458,13 @@
       <c r="L23" s="38">
         <v>100</v>
       </c>
-      <c r="M23" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N23" s="68">
+      <c r="M23" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N23" s="65">
         <v>0.1027</v>
       </c>
-      <c r="O23" s="68">
+      <c r="O23" s="65">
         <f t="shared" si="1"/>
         <v>10.27</v>
       </c>
@@ -3490,7 +3476,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D24" s="36" t="s">
@@ -3520,13 +3506,13 @@
       <c r="L24" s="36">
         <v>50</v>
       </c>
-      <c r="M24" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N24" s="66">
+      <c r="M24" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N24" s="63">
         <v>0.115</v>
       </c>
-      <c r="O24" s="66">
+      <c r="O24" s="63">
         <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
@@ -3538,7 +3524,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="58" t="s">
         <v>468</v>
       </c>
       <c r="D25" s="38" t="s">
@@ -3550,7 +3536,7 @@
       <c r="F25" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="G25" s="63" t="s">
+      <c r="G25" s="60" t="s">
         <v>287</v>
       </c>
       <c r="H25" s="38" t="s">
@@ -3568,13 +3554,13 @@
       <c r="L25" s="38">
         <v>150</v>
       </c>
-      <c r="M25" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N25" s="68">
+      <c r="M25" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N25" s="65">
         <v>0.10700000000000001</v>
       </c>
-      <c r="O25" s="68">
+      <c r="O25" s="65">
         <f t="shared" si="1"/>
         <v>16.05</v>
       </c>
@@ -3586,7 +3572,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="57" t="s">
         <v>468</v>
       </c>
       <c r="D26" s="36" t="s">
@@ -3616,13 +3602,13 @@
       <c r="L26" s="36">
         <v>100</v>
       </c>
-      <c r="M26" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N26" s="66">
+      <c r="M26" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N26" s="63">
         <v>0.1028</v>
       </c>
-      <c r="O26" s="66">
+      <c r="O26" s="63">
         <f t="shared" si="1"/>
         <v>10.280000000000001</v>
       </c>
@@ -3634,7 +3620,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="58" t="s">
         <v>469</v>
       </c>
       <c r="D27" s="38" t="s">
@@ -3664,13 +3650,13 @@
       <c r="L27" s="38">
         <v>100</v>
       </c>
-      <c r="M27" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N27" s="68">
+      <c r="M27" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N27" s="65">
         <v>0.1202</v>
       </c>
-      <c r="O27" s="68">
+      <c r="O27" s="65">
         <f t="shared" si="1"/>
         <v>12.02</v>
       </c>
@@ -3682,7 +3668,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="57" t="s">
         <v>469</v>
       </c>
       <c r="D28" s="36" t="s">
@@ -3712,13 +3698,13 @@
       <c r="L28" s="36">
         <v>100</v>
       </c>
-      <c r="M28" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N28" s="66">
+      <c r="M28" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N28" s="63">
         <v>0.11950000000000001</v>
       </c>
-      <c r="O28" s="66">
+      <c r="O28" s="63">
         <f t="shared" si="1"/>
         <v>11.950000000000001</v>
       </c>
@@ -3730,7 +3716,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="58" t="s">
         <v>469</v>
       </c>
       <c r="D29" s="38" t="s">
@@ -3760,13 +3746,13 @@
       <c r="L29" s="38">
         <v>40</v>
       </c>
-      <c r="M29" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N29" s="68">
+      <c r="M29" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N29" s="65">
         <v>0.1477</v>
       </c>
-      <c r="O29" s="68">
+      <c r="O29" s="65">
         <f t="shared" si="1"/>
         <v>5.9079999999999995</v>
       </c>
@@ -3778,7 +3764,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="60" t="s">
+      <c r="C30" s="57" t="s">
         <v>469</v>
       </c>
       <c r="D30" s="36" t="s">
@@ -3808,13 +3794,13 @@
       <c r="L30" s="36">
         <v>100</v>
       </c>
-      <c r="M30" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N30" s="66">
+      <c r="M30" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N30" s="63">
         <v>0.12920000000000001</v>
       </c>
-      <c r="O30" s="66">
+      <c r="O30" s="63">
         <f t="shared" si="1"/>
         <v>12.920000000000002</v>
       </c>
@@ -3826,7 +3812,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="58" t="s">
         <v>469</v>
       </c>
       <c r="D31" s="38" t="s">
@@ -3856,13 +3842,13 @@
       <c r="L31" s="38">
         <v>55</v>
       </c>
-      <c r="M31" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N31" s="68">
+      <c r="M31" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N31" s="65">
         <v>0.21610000000000001</v>
       </c>
-      <c r="O31" s="68">
+      <c r="O31" s="65">
         <f t="shared" si="1"/>
         <v>11.8855</v>
       </c>
@@ -3874,7 +3860,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="57" t="s">
         <v>469</v>
       </c>
       <c r="D32" s="36" t="s">
@@ -3904,13 +3890,13 @@
       <c r="L32" s="36">
         <v>35</v>
       </c>
-      <c r="M32" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N32" s="66">
+      <c r="M32" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N32" s="63">
         <v>0.18359999999999999</v>
       </c>
-      <c r="O32" s="66">
+      <c r="O32" s="63">
         <f t="shared" si="1"/>
         <v>6.4259999999999993</v>
       </c>
@@ -3922,7 +3908,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="58" t="s">
         <v>469</v>
       </c>
       <c r="D33" s="38" t="s">
@@ -3952,13 +3938,13 @@
       <c r="L33" s="38">
         <v>12</v>
       </c>
-      <c r="M33" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N33" s="68">
+      <c r="M33" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N33" s="65">
         <v>0.41849999999999998</v>
       </c>
-      <c r="O33" s="68">
+      <c r="O33" s="65">
         <f t="shared" si="1"/>
         <v>5.0220000000000002</v>
       </c>
@@ -3970,7 +3956,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="60" t="s">
+      <c r="C34" s="57" t="s">
         <v>469</v>
       </c>
       <c r="D34" s="36" t="s">
@@ -4000,13 +3986,13 @@
       <c r="L34" s="36">
         <v>20</v>
       </c>
-      <c r="M34" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N34" s="66">
+      <c r="M34" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N34" s="63">
         <v>0.13620000000000002</v>
       </c>
-      <c r="O34" s="66">
+      <c r="O34" s="63">
         <f t="shared" si="1"/>
         <v>2.7240000000000002</v>
       </c>
@@ -4018,7 +4004,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="58" t="s">
         <v>471</v>
       </c>
       <c r="D35" s="38" t="s">
@@ -4048,13 +4034,13 @@
       <c r="L35" s="38">
         <v>20</v>
       </c>
-      <c r="M35" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N35" s="68">
+      <c r="M35" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N35" s="65">
         <v>0.14900000000000002</v>
       </c>
-      <c r="O35" s="68">
+      <c r="O35" s="65">
         <f t="shared" si="1"/>
         <v>2.9800000000000004</v>
       </c>
@@ -4066,7 +4052,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="57" t="s">
         <v>472</v>
       </c>
       <c r="D36" s="36" t="s">
@@ -4096,13 +4082,13 @@
       <c r="L36" s="36">
         <v>20</v>
       </c>
-      <c r="M36" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N36" s="66">
+      <c r="M36" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N36" s="63">
         <v>0.12820000000000001</v>
       </c>
-      <c r="O36" s="66">
+      <c r="O36" s="63">
         <f t="shared" si="1"/>
         <v>2.5640000000000001</v>
       </c>
@@ -4114,7 +4100,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="58" t="s">
         <v>473</v>
       </c>
       <c r="D37" s="38" t="s">
@@ -4144,13 +4130,13 @@
       <c r="L37" s="38">
         <v>12</v>
       </c>
-      <c r="M37" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N37" s="68">
+      <c r="M37" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N37" s="65">
         <v>0.67669999999999997</v>
       </c>
-      <c r="O37" s="68">
+      <c r="O37" s="65">
         <f t="shared" si="1"/>
         <v>8.1204000000000001</v>
       </c>
@@ -4162,7 +4148,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="57" t="s">
         <v>473</v>
       </c>
       <c r="D38" s="36" t="s">
@@ -4174,7 +4160,7 @@
       <c r="F38" s="36" t="s">
         <v>467</v>
       </c>
-      <c r="G38" s="62">
+      <c r="G38" s="59">
         <v>61400416021</v>
       </c>
       <c r="H38" s="36" t="s">
@@ -4192,13 +4178,13 @@
       <c r="L38" s="36">
         <v>11</v>
       </c>
-      <c r="M38" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N38" s="66">
+      <c r="M38" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N38" s="63">
         <v>0.23469999999999999</v>
       </c>
-      <c r="O38" s="66">
+      <c r="O38" s="63">
         <f t="shared" si="1"/>
         <v>2.5817000000000001</v>
       </c>
@@ -4210,7 +4196,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="58" t="s">
         <v>473</v>
       </c>
       <c r="D39" s="38" t="s">
@@ -4240,13 +4226,13 @@
       <c r="L39" s="38">
         <v>12</v>
       </c>
-      <c r="M39" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N39" s="68">
+      <c r="M39" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N39" s="65">
         <v>0.23569999999999999</v>
       </c>
-      <c r="O39" s="68">
+      <c r="O39" s="65">
         <f t="shared" si="1"/>
         <v>2.8283999999999998</v>
       </c>
@@ -4258,7 +4244,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="60" t="s">
+      <c r="C40" s="57" t="s">
         <v>473</v>
       </c>
       <c r="D40" s="36" t="s">
@@ -4288,13 +4274,13 @@
       <c r="L40" s="36">
         <v>11</v>
       </c>
-      <c r="M40" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N40" s="66">
+      <c r="M40" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N40" s="63">
         <v>1.8351000000000002</v>
       </c>
-      <c r="O40" s="66">
+      <c r="O40" s="63">
         <f t="shared" si="1"/>
         <v>20.186100000000003</v>
       </c>
@@ -4306,7 +4292,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="58" t="s">
         <v>473</v>
       </c>
       <c r="D41" s="38" t="s">
@@ -4336,13 +4322,13 @@
       <c r="L41" s="38">
         <v>12</v>
       </c>
-      <c r="M41" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N41" s="68">
+      <c r="M41" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N41" s="65">
         <v>0.52870000000000006</v>
       </c>
-      <c r="O41" s="68">
+      <c r="O41" s="65">
         <f t="shared" si="1"/>
         <v>6.3444000000000003</v>
       </c>
@@ -4354,7 +4340,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="57" t="s">
         <v>473</v>
       </c>
       <c r="D42" s="36" t="s">
@@ -4384,13 +4370,13 @@
       <c r="L42" s="36">
         <v>25</v>
       </c>
-      <c r="M42" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N42" s="66">
+      <c r="M42" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N42" s="63">
         <v>0.1875</v>
       </c>
-      <c r="O42" s="66">
+      <c r="O42" s="63">
         <f t="shared" si="1"/>
         <v>4.6875</v>
       </c>
@@ -4402,7 +4388,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="58" t="s">
         <v>474</v>
       </c>
       <c r="D43" s="38" t="s">
@@ -4432,13 +4418,13 @@
       <c r="L43" s="38">
         <v>20</v>
       </c>
-      <c r="M43" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N43" s="68">
+      <c r="M43" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N43" s="65">
         <v>0.1447</v>
       </c>
-      <c r="O43" s="68">
+      <c r="O43" s="65">
         <f t="shared" si="1"/>
         <v>2.8940000000000001</v>
       </c>
@@ -4450,7 +4436,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="57" t="s">
         <v>473</v>
       </c>
       <c r="D44" s="36" t="s">
@@ -4480,13 +4466,13 @@
       <c r="L44" s="36">
         <v>12</v>
       </c>
-      <c r="M44" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N44" s="66">
+      <c r="M44" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N44" s="63">
         <v>0.40129999999999999</v>
       </c>
-      <c r="O44" s="66">
+      <c r="O44" s="63">
         <f t="shared" si="1"/>
         <v>4.8155999999999999</v>
       </c>
@@ -4498,7 +4484,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="58" t="s">
         <v>473</v>
       </c>
       <c r="D45" s="38" t="s">
@@ -4528,13 +4514,13 @@
       <c r="L45" s="38">
         <v>12</v>
       </c>
-      <c r="M45" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N45" s="68">
+      <c r="M45" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N45" s="65">
         <v>0.76449999999999996</v>
       </c>
-      <c r="O45" s="68">
+      <c r="O45" s="65">
         <f t="shared" si="1"/>
         <v>9.1739999999999995</v>
       </c>
@@ -4546,7 +4532,7 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="57" t="s">
         <v>473</v>
       </c>
       <c r="D46" s="36" t="s">
@@ -4576,13 +4562,13 @@
       <c r="L46" s="36">
         <v>12</v>
       </c>
-      <c r="M46" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N46" s="66">
+      <c r="M46" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N46" s="63">
         <v>0.27039999999999997</v>
       </c>
-      <c r="O46" s="66">
+      <c r="O46" s="63">
         <f t="shared" si="1"/>
         <v>3.2447999999999997</v>
       </c>
@@ -4594,7 +4580,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="58" t="s">
         <v>474</v>
       </c>
       <c r="D47" s="38" t="s">
@@ -4624,13 +4610,13 @@
       <c r="L47" s="38">
         <v>20</v>
       </c>
-      <c r="M47" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N47" s="68">
+      <c r="M47" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N47" s="65">
         <v>0.1515</v>
       </c>
-      <c r="O47" s="68">
+      <c r="O47" s="65">
         <f t="shared" si="1"/>
         <v>3.03</v>
       </c>
@@ -4642,7 +4628,7 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="57" t="s">
         <v>475</v>
       </c>
       <c r="D48" s="36" t="s">
@@ -4672,13 +4658,13 @@
       <c r="L48" s="36">
         <v>30</v>
       </c>
-      <c r="M48" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N48" s="66">
+      <c r="M48" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N48" s="63">
         <v>0.16090000000000002</v>
       </c>
-      <c r="O48" s="66">
+      <c r="O48" s="63">
         <f t="shared" si="1"/>
         <v>4.8270000000000008</v>
       </c>
@@ -4690,7 +4676,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="58" t="s">
         <v>475</v>
       </c>
       <c r="D49" s="38" t="s">
@@ -4720,13 +4706,13 @@
       <c r="L49" s="38">
         <v>12</v>
       </c>
-      <c r="M49" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N49" s="68">
+      <c r="M49" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N49" s="65">
         <v>0.24030000000000001</v>
       </c>
-      <c r="O49" s="68">
+      <c r="O49" s="65">
         <f t="shared" si="1"/>
         <v>2.8836000000000004</v>
       </c>
@@ -4738,7 +4724,7 @@
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="57" t="s">
         <v>475</v>
       </c>
       <c r="D50" s="36" t="s">
@@ -4768,13 +4754,13 @@
       <c r="L50" s="36">
         <v>30</v>
       </c>
-      <c r="M50" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N50" s="66">
+      <c r="M50" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N50" s="63">
         <v>0.14380000000000001</v>
       </c>
-      <c r="O50" s="66">
+      <c r="O50" s="63">
         <f t="shared" si="1"/>
         <v>4.3140000000000001</v>
       </c>
@@ -4786,7 +4772,7 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="58" t="s">
         <v>475</v>
       </c>
       <c r="D51" s="38" t="s">
@@ -4816,13 +4802,13 @@
       <c r="L51" s="38">
         <v>22</v>
       </c>
-      <c r="M51" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N51" s="68">
+      <c r="M51" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N51" s="65">
         <v>0.23650000000000002</v>
       </c>
-      <c r="O51" s="68">
+      <c r="O51" s="65">
         <f t="shared" si="1"/>
         <v>5.2030000000000003</v>
       </c>
@@ -4834,7 +4820,7 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="60" t="s">
+      <c r="C52" s="57" t="s">
         <v>475</v>
       </c>
       <c r="D52" s="36" t="s">
@@ -4864,13 +4850,13 @@
       <c r="L52" s="36">
         <v>22</v>
       </c>
-      <c r="M52" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N52" s="66">
+      <c r="M52" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N52" s="63">
         <v>0.248</v>
       </c>
-      <c r="O52" s="66">
+      <c r="O52" s="63">
         <f t="shared" si="1"/>
         <v>5.4559999999999995</v>
       </c>
@@ -4882,7 +4868,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="58" t="s">
         <v>475</v>
       </c>
       <c r="D53" s="38" t="s">
@@ -4912,13 +4898,13 @@
       <c r="L53" s="38">
         <v>20</v>
       </c>
-      <c r="M53" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N53" s="68">
+      <c r="M53" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N53" s="65">
         <v>0.1706</v>
       </c>
-      <c r="O53" s="68">
+      <c r="O53" s="65">
         <f t="shared" si="1"/>
         <v>3.4119999999999999</v>
       </c>
@@ -4930,7 +4916,7 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="60" t="s">
+      <c r="C54" s="57" t="s">
         <v>472</v>
       </c>
       <c r="D54" s="36" t="s">
@@ -4960,13 +4946,13 @@
       <c r="L54" s="36">
         <v>100</v>
       </c>
-      <c r="M54" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N54" s="66">
+      <c r="M54" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N54" s="63">
         <v>0.10310000000000001</v>
       </c>
-      <c r="O54" s="66">
+      <c r="O54" s="63">
         <f t="shared" si="1"/>
         <v>10.31</v>
       </c>
@@ -4978,7 +4964,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="61" t="s">
+      <c r="C55" s="58" t="s">
         <v>475</v>
       </c>
       <c r="D55" s="38" t="s">
@@ -5008,13 +4994,13 @@
       <c r="L55" s="38">
         <v>20</v>
       </c>
-      <c r="M55" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N55" s="68">
+      <c r="M55" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N55" s="65">
         <v>0.15620000000000001</v>
       </c>
-      <c r="O55" s="68">
+      <c r="O55" s="65">
         <f t="shared" si="1"/>
         <v>3.1240000000000001</v>
       </c>
@@ -5026,7 +5012,7 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="60" t="s">
+      <c r="C56" s="57" t="s">
         <v>476</v>
       </c>
       <c r="D56" s="36" t="s">
@@ -5038,7 +5024,7 @@
       <c r="F56" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="G56" s="62" t="s">
+      <c r="G56" s="59" t="s">
         <v>477</v>
       </c>
       <c r="H56" s="36" t="s">
@@ -5056,13 +5042,13 @@
       <c r="L56" s="36">
         <v>50</v>
       </c>
-      <c r="M56" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N56" s="66">
+      <c r="M56" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N56" s="63">
         <v>0.1163</v>
       </c>
-      <c r="O56" s="66">
+      <c r="O56" s="63">
         <f t="shared" si="1"/>
         <v>5.8150000000000004</v>
       </c>
@@ -5074,7 +5060,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="61" t="s">
+      <c r="C57" s="58" t="s">
         <v>478</v>
       </c>
       <c r="D57" s="38" t="s">
@@ -5086,7 +5072,7 @@
       <c r="F57" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="G57" s="63" t="s">
+      <c r="G57" s="60" t="s">
         <v>308</v>
       </c>
       <c r="H57" s="38" t="s">
@@ -5104,13 +5090,13 @@
       <c r="L57" s="38">
         <v>20</v>
       </c>
-      <c r="M57" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N57" s="68">
+      <c r="M57" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N57" s="65">
         <v>0.13540000000000002</v>
       </c>
-      <c r="O57" s="68">
+      <c r="O57" s="65">
         <f t="shared" si="1"/>
         <v>2.7080000000000002</v>
       </c>
@@ -5122,7 +5108,7 @@
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="60" t="s">
+      <c r="C58" s="57" t="s">
         <v>476</v>
       </c>
       <c r="D58" s="36" t="s">
@@ -5134,7 +5120,7 @@
       <c r="F58" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="59" t="s">
         <v>309</v>
       </c>
       <c r="H58" s="36" t="s">
@@ -5152,13 +5138,13 @@
       <c r="L58" s="36">
         <v>20</v>
       </c>
-      <c r="M58" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N58" s="66">
+      <c r="M58" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N58" s="63">
         <v>0.13520000000000001</v>
       </c>
-      <c r="O58" s="66">
+      <c r="O58" s="63">
         <f t="shared" si="1"/>
         <v>2.7040000000000002</v>
       </c>
@@ -5170,7 +5156,7 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="61" t="s">
+      <c r="C59" s="58" t="s">
         <v>478</v>
       </c>
       <c r="D59" s="38" t="s">
@@ -5182,7 +5168,7 @@
       <c r="F59" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="G59" s="63" t="s">
+      <c r="G59" s="60" t="s">
         <v>310</v>
       </c>
       <c r="H59" s="38" t="s">
@@ -5200,11 +5186,11 @@
       <c r="L59" s="38">
         <v>50</v>
       </c>
-      <c r="M59" s="67"/>
-      <c r="N59" s="68">
+      <c r="M59" s="64"/>
+      <c r="N59" s="65">
         <v>0.1159</v>
       </c>
-      <c r="O59" s="68">
+      <c r="O59" s="65">
         <f t="shared" si="1"/>
         <v>5.7949999999999999</v>
       </c>
@@ -5216,7 +5202,7 @@
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="60" t="s">
+      <c r="C60" s="57" t="s">
         <v>479</v>
       </c>
       <c r="D60" s="36" t="s">
@@ -5246,13 +5232,13 @@
       <c r="L60" s="36" t="s">
         <v>480</v>
       </c>
-      <c r="M60" s="65" t="s">
-        <v>480</v>
-      </c>
-      <c r="N60" s="66">
+      <c r="M60" s="62" t="s">
+        <v>480</v>
+      </c>
+      <c r="N60" s="63">
         <v>0</v>
       </c>
-      <c r="O60" s="66" t="s">
+      <c r="O60" s="63" t="s">
         <v>480</v>
       </c>
       <c r="P60" s="36"/>
@@ -5263,7 +5249,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="61" t="s">
+      <c r="C61" s="58" t="s">
         <v>474</v>
       </c>
       <c r="D61" s="38" t="s">
@@ -5275,7 +5261,7 @@
       <c r="F61" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="G61" s="63">
+      <c r="G61" s="60">
         <v>61300211121</v>
       </c>
       <c r="H61" s="38" t="s">
@@ -5293,13 +5279,13 @@
       <c r="L61" s="38">
         <v>150</v>
       </c>
-      <c r="M61" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N61" s="68">
+      <c r="M61" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N61" s="65">
         <v>0.11360000000000001</v>
       </c>
-      <c r="O61" s="68">
+      <c r="O61" s="65">
         <f t="shared" si="1"/>
         <v>17.040000000000003</v>
       </c>
@@ -5311,7 +5297,7 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="60" t="s">
+      <c r="C62" s="57" t="s">
         <v>474</v>
       </c>
       <c r="D62" s="36" t="s">
@@ -5323,7 +5309,7 @@
       <c r="F62" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="G62" s="62">
+      <c r="G62" s="59">
         <v>61300611121</v>
       </c>
       <c r="H62" s="36" t="s">
@@ -5341,13 +5327,13 @@
       <c r="L62" s="36">
         <v>20</v>
       </c>
-      <c r="M62" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N62" s="66">
+      <c r="M62" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N62" s="63">
         <v>0.13150000000000001</v>
       </c>
-      <c r="O62" s="66">
+      <c r="O62" s="63">
         <f t="shared" si="1"/>
         <v>2.63</v>
       </c>
@@ -5359,7 +5345,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="C63" s="58" t="s">
         <v>474</v>
       </c>
       <c r="D63" s="38" t="s">
@@ -5371,7 +5357,7 @@
       <c r="F63" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="G63" s="63">
+      <c r="G63" s="60">
         <v>61300311121</v>
       </c>
       <c r="H63" s="38" t="s">
@@ -5389,13 +5375,13 @@
       <c r="L63" s="38">
         <v>50</v>
       </c>
-      <c r="M63" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N63" s="68">
+      <c r="M63" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N63" s="65">
         <v>0.11650000000000001</v>
       </c>
-      <c r="O63" s="68">
+      <c r="O63" s="65">
         <f t="shared" si="1"/>
         <v>5.8250000000000002</v>
       </c>
@@ -5407,7 +5393,7 @@
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
-      <c r="C64" s="60" t="s">
+      <c r="C64" s="57" t="s">
         <v>481</v>
       </c>
       <c r="D64" s="36" t="s">
@@ -5437,13 +5423,13 @@
       <c r="L64" s="36">
         <v>20</v>
       </c>
-      <c r="M64" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N64" s="66">
+      <c r="M64" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N64" s="63">
         <v>0.13670000000000002</v>
       </c>
-      <c r="O64" s="66">
+      <c r="O64" s="63">
         <f t="shared" si="1"/>
         <v>2.7340000000000004</v>
       </c>
@@ -5455,7 +5441,7 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="61" t="s">
+      <c r="C65" s="58" t="s">
         <v>481</v>
       </c>
       <c r="D65" s="38" t="s">
@@ -5485,13 +5471,13 @@
       <c r="L65" s="38">
         <v>60</v>
       </c>
-      <c r="M65" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N65" s="68">
+      <c r="M65" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N65" s="65">
         <v>0.12050000000000001</v>
       </c>
-      <c r="O65" s="68">
+      <c r="O65" s="65">
         <f t="shared" si="1"/>
         <v>7.23</v>
       </c>
@@ -5503,7 +5489,7 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="60" t="s">
+      <c r="C66" s="57" t="s">
         <v>481</v>
       </c>
       <c r="D66" s="36" t="s">
@@ -5533,13 +5519,13 @@
       <c r="L66" s="36">
         <v>40</v>
       </c>
-      <c r="M66" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N66" s="66">
+      <c r="M66" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N66" s="63">
         <v>0.13140000000000002</v>
       </c>
-      <c r="O66" s="66">
+      <c r="O66" s="63">
         <f t="shared" si="1"/>
         <v>5.2560000000000002</v>
       </c>
@@ -5551,7 +5537,7 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="61" t="s">
+      <c r="C67" s="58" t="s">
         <v>481</v>
       </c>
       <c r="D67" s="38" t="s">
@@ -5581,13 +5567,13 @@
       <c r="L67" s="38">
         <v>20</v>
       </c>
-      <c r="M67" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N67" s="68">
+      <c r="M67" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N67" s="65">
         <v>0.14960000000000001</v>
       </c>
-      <c r="O67" s="68">
+      <c r="O67" s="65">
         <f t="shared" si="1"/>
         <v>2.992</v>
       </c>
@@ -5599,7 +5585,7 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="60" t="s">
+      <c r="C68" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D68" s="36" t="s">
@@ -5629,13 +5615,13 @@
       <c r="L68" s="36">
         <v>400</v>
       </c>
-      <c r="M68" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N68" s="66">
+      <c r="M68" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N68" s="63">
         <v>0.1017</v>
       </c>
-      <c r="O68" s="66">
+      <c r="O68" s="63">
         <f t="shared" si="1"/>
         <v>40.68</v>
       </c>
@@ -5647,7 +5633,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="61" t="s">
+      <c r="C69" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D69" s="38" t="s">
@@ -5677,13 +5663,13 @@
       <c r="L69" s="38">
         <v>80</v>
       </c>
-      <c r="M69" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N69" s="68">
+      <c r="M69" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N69" s="65">
         <v>0.13270000000000001</v>
       </c>
-      <c r="O69" s="68">
+      <c r="O69" s="65">
         <f t="shared" si="1"/>
         <v>10.616000000000001</v>
       </c>
@@ -5695,7 +5681,7 @@
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="60" t="s">
+      <c r="C70" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D70" s="36" t="s">
@@ -5725,13 +5711,13 @@
       <c r="L70" s="36">
         <v>50</v>
       </c>
-      <c r="M70" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N70" s="66">
+      <c r="M70" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N70" s="63">
         <v>0.11330000000000001</v>
       </c>
-      <c r="O70" s="66">
+      <c r="O70" s="63">
         <f t="shared" si="1"/>
         <v>5.6650000000000009</v>
       </c>
@@ -5743,7 +5729,7 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="61" t="s">
+      <c r="C71" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D71" s="38" t="s">
@@ -5773,13 +5759,13 @@
       <c r="L71" s="38">
         <v>20</v>
       </c>
-      <c r="M71" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N71" s="68">
+      <c r="M71" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N71" s="65">
         <v>0.12590000000000001</v>
       </c>
-      <c r="O71" s="68">
+      <c r="O71" s="65">
         <f t="shared" si="1"/>
         <v>2.5180000000000002</v>
       </c>
@@ -5791,7 +5777,7 @@
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="60" t="s">
+      <c r="C72" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D72" s="36" t="s">
@@ -5821,13 +5807,13 @@
       <c r="L72" s="36">
         <v>20</v>
       </c>
-      <c r="M72" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N72" s="66">
+      <c r="M72" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N72" s="63">
         <v>0.12859999999999999</v>
       </c>
-      <c r="O72" s="66">
+      <c r="O72" s="63">
         <f t="shared" si="1"/>
         <v>2.5720000000000001</v>
       </c>
@@ -5839,7 +5825,7 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="61" t="s">
+      <c r="C73" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D73" s="38" t="s">
@@ -5869,13 +5855,13 @@
       <c r="L73" s="38">
         <v>100</v>
       </c>
-      <c r="M73" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N73" s="68">
+      <c r="M73" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N73" s="65">
         <v>0.1014</v>
       </c>
-      <c r="O73" s="68">
+      <c r="O73" s="65">
         <f t="shared" si="1"/>
         <v>10.14</v>
       </c>
@@ -5887,7 +5873,7 @@
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="60" t="s">
+      <c r="C74" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D74" s="36" t="s">
@@ -5917,13 +5903,13 @@
       <c r="L74" s="36">
         <v>100</v>
       </c>
-      <c r="M74" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N74" s="66">
+      <c r="M74" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N74" s="63">
         <v>0.10120000000000001</v>
       </c>
-      <c r="O74" s="66">
+      <c r="O74" s="63">
         <f t="shared" si="1"/>
         <v>10.120000000000001</v>
       </c>
@@ -5935,7 +5921,7 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="61" t="s">
+      <c r="C75" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D75" s="38" t="s">
@@ -5947,7 +5933,7 @@
       <c r="F75" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="G75" s="64" t="s">
+      <c r="G75" s="61" t="s">
         <v>321</v>
       </c>
       <c r="H75" s="38" t="s">
@@ -5965,14 +5951,14 @@
       <c r="L75" s="38">
         <v>100</v>
       </c>
-      <c r="M75" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N75" s="68">
+      <c r="M75" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N75" s="65">
         <v>0.10110000000000001</v>
       </c>
-      <c r="O75" s="68">
-        <f t="shared" ref="O75:O124" si="2">N75*L75</f>
+      <c r="O75" s="65">
+        <f t="shared" ref="O75:O119" si="2">N75*L75</f>
         <v>10.110000000000001</v>
       </c>
       <c r="P75" s="38"/>
@@ -5983,7 +5969,7 @@
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="60" t="s">
+      <c r="C76" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D76" s="36" t="s">
@@ -6013,13 +5999,13 @@
       <c r="L76" s="36">
         <v>20</v>
       </c>
-      <c r="M76" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N76" s="66">
+      <c r="M76" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N76" s="63">
         <v>0.12590000000000001</v>
       </c>
-      <c r="O76" s="66">
+      <c r="O76" s="63">
         <f t="shared" si="2"/>
         <v>2.5180000000000002</v>
       </c>
@@ -6031,7 +6017,7 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="61" t="s">
+      <c r="C77" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D77" s="38" t="s">
@@ -6061,13 +6047,13 @@
       <c r="L77" s="38">
         <v>100</v>
       </c>
-      <c r="M77" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N77" s="68">
+      <c r="M77" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N77" s="65">
         <v>0.1013</v>
       </c>
-      <c r="O77" s="68">
+      <c r="O77" s="65">
         <f t="shared" si="2"/>
         <v>10.130000000000001</v>
       </c>
@@ -6079,7 +6065,7 @@
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="60" t="s">
+      <c r="C78" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D78" s="36" t="s">
@@ -6109,13 +6095,13 @@
       <c r="L78" s="36">
         <v>200</v>
       </c>
-      <c r="M78" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N78" s="66">
+      <c r="M78" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N78" s="63">
         <v>0.10100000000000001</v>
       </c>
-      <c r="O78" s="66">
+      <c r="O78" s="63">
         <f t="shared" si="2"/>
         <v>20.200000000000003</v>
       </c>
@@ -6127,7 +6113,7 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="61" t="s">
+      <c r="C79" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D79" s="38" t="s">
@@ -6157,13 +6143,13 @@
       <c r="L79" s="38">
         <v>100</v>
       </c>
-      <c r="M79" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N79" s="68">
+      <c r="M79" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N79" s="65">
         <v>0.10310000000000001</v>
       </c>
-      <c r="O79" s="68">
+      <c r="O79" s="65">
         <f t="shared" si="2"/>
         <v>10.31</v>
       </c>
@@ -6175,7 +6161,7 @@
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="60" t="s">
+      <c r="C80" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D80" s="36" t="s">
@@ -6205,13 +6191,13 @@
       <c r="L80" s="36">
         <v>100</v>
       </c>
-      <c r="M80" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N80" s="66">
+      <c r="M80" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N80" s="63">
         <v>0.1009</v>
       </c>
-      <c r="O80" s="66">
+      <c r="O80" s="63">
         <f t="shared" si="2"/>
         <v>10.09</v>
       </c>
@@ -6223,7 +6209,7 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="61" t="s">
+      <c r="C81" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D81" s="38" t="s">
@@ -6253,13 +6239,13 @@
       <c r="L81" s="38">
         <v>20</v>
       </c>
-      <c r="M81" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N81" s="68">
+      <c r="M81" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N81" s="65">
         <v>0.11940000000000001</v>
       </c>
-      <c r="O81" s="68">
+      <c r="O81" s="65">
         <f t="shared" si="2"/>
         <v>2.3879999999999999</v>
       </c>
@@ -6271,7 +6257,7 @@
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="60" t="s">
+      <c r="C82" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D82" s="36" t="s">
@@ -6301,13 +6287,13 @@
       <c r="L82" s="36">
         <v>100</v>
       </c>
-      <c r="M82" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N82" s="66">
+      <c r="M82" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N82" s="63">
         <v>0.10200000000000001</v>
       </c>
-      <c r="O82" s="66">
+      <c r="O82" s="63">
         <f t="shared" si="2"/>
         <v>10.200000000000001</v>
       </c>
@@ -6319,7 +6305,7 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="61" t="s">
+      <c r="C83" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D83" s="38" t="s">
@@ -6349,13 +6335,13 @@
       <c r="L83" s="38">
         <v>200</v>
       </c>
-      <c r="M83" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N83" s="68">
+      <c r="M83" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N83" s="65">
         <v>0.1008</v>
       </c>
-      <c r="O83" s="68">
+      <c r="O83" s="65">
         <f t="shared" si="2"/>
         <v>20.16</v>
       </c>
@@ -6367,7 +6353,7 @@
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="60" t="s">
+      <c r="C84" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D84" s="36" t="s">
@@ -6397,13 +6383,13 @@
       <c r="L84" s="36">
         <v>50</v>
       </c>
-      <c r="M84" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N84" s="66">
+      <c r="M84" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N84" s="63">
         <v>0.10680000000000001</v>
       </c>
-      <c r="O84" s="66">
+      <c r="O84" s="63">
         <f t="shared" si="2"/>
         <v>5.34</v>
       </c>
@@ -6415,7 +6401,7 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="61" t="s">
+      <c r="C85" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D85" s="38" t="s">
@@ -6445,13 +6431,13 @@
       <c r="L85" s="38">
         <v>100</v>
       </c>
-      <c r="M85" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N85" s="68">
+      <c r="M85" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N85" s="65">
         <v>0.11430000000000001</v>
       </c>
-      <c r="O85" s="68">
+      <c r="O85" s="65">
         <f t="shared" si="2"/>
         <v>11.430000000000001</v>
       </c>
@@ -6463,7 +6449,7 @@
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="60" t="s">
+      <c r="C86" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D86" s="36" t="s">
@@ -6493,13 +6479,13 @@
       <c r="L86" s="36">
         <v>100</v>
       </c>
-      <c r="M86" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N86" s="66">
+      <c r="M86" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N86" s="63">
         <v>0.10300000000000001</v>
       </c>
-      <c r="O86" s="66">
+      <c r="O86" s="63">
         <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
@@ -6511,7 +6497,7 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="61" t="s">
+      <c r="C87" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D87" s="38" t="s">
@@ -6541,13 +6527,13 @@
       <c r="L87" s="38">
         <v>40</v>
       </c>
-      <c r="M87" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N87" s="68">
+      <c r="M87" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N87" s="65">
         <v>0.12570000000000001</v>
       </c>
-      <c r="O87" s="68">
+      <c r="O87" s="65">
         <f t="shared" si="2"/>
         <v>5.0280000000000005</v>
       </c>
@@ -6559,7 +6545,7 @@
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="60" t="s">
+      <c r="C88" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D88" s="36" t="s">
@@ -6589,13 +6575,13 @@
       <c r="L88" s="36">
         <v>100</v>
       </c>
-      <c r="M88" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N88" s="66">
+      <c r="M88" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N88" s="63">
         <v>0.10400000000000001</v>
       </c>
-      <c r="O88" s="66">
+      <c r="O88" s="63">
         <f t="shared" si="2"/>
         <v>10.4</v>
       </c>
@@ -6607,7 +6593,7 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="61" t="s">
+      <c r="C89" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D89" s="38" t="s">
@@ -6619,7 +6605,7 @@
       <c r="F89" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="G89" s="64" t="s">
+      <c r="G89" s="61" t="s">
         <v>334</v>
       </c>
       <c r="H89" s="38" t="s">
@@ -6637,13 +6623,13 @@
       <c r="L89" s="38">
         <v>100</v>
       </c>
-      <c r="M89" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N89" s="68">
+      <c r="M89" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N89" s="65">
         <v>0.10110000000000001</v>
       </c>
-      <c r="O89" s="68">
+      <c r="O89" s="65">
         <f t="shared" si="2"/>
         <v>10.110000000000001</v>
       </c>
@@ -6655,7 +6641,7 @@
         <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
-      <c r="C90" s="60" t="s">
+      <c r="C90" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D90" s="36" t="s">
@@ -6685,13 +6671,13 @@
       <c r="L90" s="36">
         <v>100</v>
       </c>
-      <c r="M90" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N90" s="66">
+      <c r="M90" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N90" s="63">
         <v>0.10110000000000001</v>
       </c>
-      <c r="O90" s="66">
+      <c r="O90" s="63">
         <f t="shared" si="2"/>
         <v>10.110000000000001</v>
       </c>
@@ -6703,7 +6689,7 @@
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="61" t="s">
+      <c r="C91" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D91" s="38" t="s">
@@ -6733,13 +6719,13 @@
       <c r="L91" s="38">
         <v>100</v>
       </c>
-      <c r="M91" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N91" s="68">
+      <c r="M91" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N91" s="65">
         <v>0.1013</v>
       </c>
-      <c r="O91" s="68">
+      <c r="O91" s="65">
         <f t="shared" si="2"/>
         <v>10.130000000000001</v>
       </c>
@@ -6751,7 +6737,7 @@
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="60" t="s">
+      <c r="C92" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D92" s="36" t="s">
@@ -6781,13 +6767,13 @@
       <c r="L92" s="36">
         <v>100</v>
       </c>
-      <c r="M92" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N92" s="66">
+      <c r="M92" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N92" s="63">
         <v>0.1014</v>
       </c>
-      <c r="O92" s="66">
+      <c r="O92" s="63">
         <f t="shared" si="2"/>
         <v>10.14</v>
       </c>
@@ -6799,7 +6785,7 @@
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C93" s="61" t="s">
+      <c r="C93" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D93" s="38" t="s">
@@ -6829,13 +6815,13 @@
       <c r="L93" s="38">
         <v>100</v>
       </c>
-      <c r="M93" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N93" s="68">
+      <c r="M93" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N93" s="65">
         <v>0.1014</v>
       </c>
-      <c r="O93" s="68">
+      <c r="O93" s="65">
         <f t="shared" si="2"/>
         <v>10.14</v>
       </c>
@@ -6847,7 +6833,7 @@
         <f>ROW(B94) - ROW($B$9)</f>
         <v>85</v>
       </c>
-      <c r="C94" s="60" t="s">
+      <c r="C94" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D94" s="36" t="s">
@@ -6877,13 +6863,13 @@
       <c r="L94" s="36">
         <v>100</v>
       </c>
-      <c r="M94" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N94" s="66">
+      <c r="M94" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N94" s="63">
         <v>0.10120000000000001</v>
       </c>
-      <c r="O94" s="66">
+      <c r="O94" s="63">
         <f t="shared" si="2"/>
         <v>10.120000000000001</v>
       </c>
@@ -6895,7 +6881,7 @@
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C95" s="61" t="s">
+      <c r="C95" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D95" s="38" t="s">
@@ -6925,13 +6911,13 @@
       <c r="L95" s="38">
         <v>45</v>
       </c>
-      <c r="M95" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N95" s="68">
+      <c r="M95" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N95" s="65">
         <v>0.1855</v>
       </c>
-      <c r="O95" s="68">
+      <c r="O95" s="65">
         <f t="shared" si="2"/>
         <v>8.3475000000000001</v>
       </c>
@@ -6943,7 +6929,7 @@
         <f>ROW(B96) - ROW($B$9)</f>
         <v>87</v>
       </c>
-      <c r="C96" s="60" t="s">
+      <c r="C96" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D96" s="36" t="s">
@@ -6973,13 +6959,13 @@
       <c r="L96" s="36">
         <v>50</v>
       </c>
-      <c r="M96" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N96" s="66">
+      <c r="M96" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N96" s="63">
         <v>0.10490000000000001</v>
       </c>
-      <c r="O96" s="66">
+      <c r="O96" s="63">
         <f t="shared" si="2"/>
         <v>5.2450000000000001</v>
       </c>
@@ -6991,7 +6977,7 @@
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C97" s="61" t="s">
+      <c r="C97" s="58" t="s">
         <v>482</v>
       </c>
       <c r="D97" s="38" t="s">
@@ -7021,13 +7007,13 @@
       <c r="L97" s="38">
         <v>100</v>
       </c>
-      <c r="M97" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N97" s="68">
+      <c r="M97" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N97" s="65">
         <v>0.1014</v>
       </c>
-      <c r="O97" s="68">
+      <c r="O97" s="65">
         <f t="shared" si="2"/>
         <v>10.14</v>
       </c>
@@ -7039,7 +7025,7 @@
         <f>ROW(B98) - ROW($B$9)</f>
         <v>89</v>
       </c>
-      <c r="C98" s="60" t="s">
+      <c r="C98" s="57" t="s">
         <v>482</v>
       </c>
       <c r="D98" s="36" t="s">
@@ -7069,13 +7055,13 @@
       <c r="L98" s="36">
         <v>20</v>
       </c>
-      <c r="M98" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N98" s="66">
+      <c r="M98" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N98" s="63">
         <v>0.1361</v>
       </c>
-      <c r="O98" s="66">
+      <c r="O98" s="63">
         <f t="shared" si="2"/>
         <v>2.722</v>
       </c>
@@ -7087,7 +7073,7 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C99" s="61" t="s">
+      <c r="C99" s="58" t="s">
         <v>264</v>
       </c>
       <c r="D99" s="38" t="s">
@@ -7117,13 +7103,13 @@
       <c r="L99" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="M99" s="67" t="s">
-        <v>480</v>
-      </c>
-      <c r="N99" s="68">
+      <c r="M99" s="64" t="s">
+        <v>480</v>
+      </c>
+      <c r="N99" s="65">
         <v>0</v>
       </c>
-      <c r="O99" s="68" t="s">
+      <c r="O99" s="65" t="s">
         <v>480</v>
       </c>
       <c r="P99" s="38"/>
@@ -7134,7 +7120,7 @@
         <f>ROW(B100) - ROW($B$9)</f>
         <v>91</v>
       </c>
-      <c r="C100" s="60" t="s">
+      <c r="C100" s="57" t="s">
         <v>485</v>
       </c>
       <c r="D100" s="36" t="s">
@@ -7164,13 +7150,13 @@
       <c r="L100" s="36">
         <v>80</v>
       </c>
-      <c r="M100" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N100" s="66">
+      <c r="M100" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N100" s="63">
         <v>0.1595</v>
       </c>
-      <c r="O100" s="66">
+      <c r="O100" s="63">
         <f t="shared" si="2"/>
         <v>12.76</v>
       </c>
@@ -7182,43 +7168,45 @@
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C101" s="61" t="s">
+      <c r="C101" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D101" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="E101" s="73" t="s">
+      <c r="E101" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="F101" s="74" t="s">
+      <c r="F101" s="76" t="s">
         <v>487</v>
       </c>
-      <c r="G101" s="73" t="s">
+      <c r="G101" s="75" t="s">
         <v>266</v>
       </c>
-      <c r="H101" s="74"/>
-      <c r="I101" s="74" t="s">
+      <c r="H101" s="76"/>
+      <c r="I101" s="76" t="s">
         <v>393</v>
       </c>
-      <c r="J101" s="74" t="s">
-        <v>480</v>
-      </c>
-      <c r="K101" s="73">
+      <c r="J101" s="76" t="s">
+        <v>480</v>
+      </c>
+      <c r="K101" s="75">
         <v>1</v>
       </c>
-      <c r="L101" s="74"/>
-      <c r="M101" s="75" t="s">
-        <v>514</v>
-      </c>
-      <c r="N101" s="68">
-        <v>0.1</v>
-      </c>
-      <c r="O101" s="76">
+      <c r="L101" s="76">
+        <v>11</v>
+      </c>
+      <c r="M101" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N101" s="65">
+        <v>0.3</v>
+      </c>
+      <c r="O101" s="77">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P101" s="74"/>
+        <v>3.3</v>
+      </c>
+      <c r="P101" s="68"/>
     </row>
     <row r="102" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
@@ -7226,7 +7214,7 @@
         <f>ROW(B102) - ROW($B$9)</f>
         <v>93</v>
       </c>
-      <c r="C102" s="60" t="s">
+      <c r="C102" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D102" s="36" t="s">
@@ -7256,13 +7244,13 @@
       <c r="L102" s="36">
         <v>12</v>
       </c>
-      <c r="M102" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N102" s="66">
+      <c r="M102" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N102" s="63">
         <v>0.66289999999999993</v>
       </c>
-      <c r="O102" s="66">
+      <c r="O102" s="63">
         <f t="shared" si="2"/>
         <v>7.9547999999999988</v>
       </c>
@@ -7274,7 +7262,7 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="C103" s="61" t="s">
+      <c r="C103" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D103" s="38" t="s">
@@ -7304,13 +7292,13 @@
       <c r="L103" s="38">
         <v>22</v>
       </c>
-      <c r="M103" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N103" s="68">
+      <c r="M103" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N103" s="65">
         <v>0.25480000000000003</v>
       </c>
-      <c r="O103" s="68">
+      <c r="O103" s="65">
         <f t="shared" si="2"/>
         <v>5.6056000000000008</v>
       </c>
@@ -7322,7 +7310,7 @@
         <f>ROW(B104) - ROW($B$9)</f>
         <v>95</v>
       </c>
-      <c r="C104" s="60" t="s">
+      <c r="C104" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D104" s="36" t="s">
@@ -7352,13 +7340,13 @@
       <c r="L104" s="36">
         <v>11</v>
       </c>
-      <c r="M104" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N104" s="66">
+      <c r="M104" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N104" s="63">
         <v>0.25559999999999999</v>
       </c>
-      <c r="O104" s="66">
+      <c r="O104" s="63">
         <f t="shared" si="2"/>
         <v>2.8115999999999999</v>
       </c>
@@ -7370,7 +7358,7 @@
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C105" s="61" t="s">
+      <c r="C105" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D105" s="38" t="s">
@@ -7400,13 +7388,13 @@
       <c r="L105" s="38">
         <v>12</v>
       </c>
-      <c r="M105" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N105" s="68">
+      <c r="M105" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N105" s="65">
         <v>0.29189999999999999</v>
       </c>
-      <c r="O105" s="68">
+      <c r="O105" s="65">
         <f t="shared" si="2"/>
         <v>3.5027999999999997</v>
       </c>
@@ -7418,7 +7406,7 @@
         <f>ROW(B106) - ROW($B$9)</f>
         <v>97</v>
       </c>
-      <c r="C106" s="60" t="s">
+      <c r="C106" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D106" s="36" t="s">
@@ -7448,13 +7436,13 @@
       <c r="L106" s="36">
         <v>15</v>
       </c>
-      <c r="M106" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N106" s="66">
+      <c r="M106" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N106" s="63">
         <v>0.23039999999999999</v>
       </c>
-      <c r="O106" s="66">
+      <c r="O106" s="63">
         <f t="shared" si="2"/>
         <v>3.456</v>
       </c>
@@ -7466,7 +7454,7 @@
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="C107" s="61" t="s">
+      <c r="C107" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D107" s="38" t="s">
@@ -7496,13 +7484,13 @@
       <c r="L107" s="38">
         <v>12</v>
       </c>
-      <c r="M107" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N107" s="68">
+      <c r="M107" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N107" s="65">
         <v>0.41849999999999998</v>
       </c>
-      <c r="O107" s="68">
+      <c r="O107" s="65">
         <f t="shared" si="2"/>
         <v>5.0220000000000002</v>
       </c>
@@ -7514,7 +7502,7 @@
         <f>ROW(B108) - ROW($B$9)</f>
         <v>99</v>
       </c>
-      <c r="C108" s="60" t="s">
+      <c r="C108" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D108" s="36" t="s">
@@ -7544,13 +7532,13 @@
       <c r="L108" s="36">
         <v>11</v>
       </c>
-      <c r="M108" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N108" s="66">
+      <c r="M108" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N108" s="63">
         <v>2.06</v>
       </c>
-      <c r="O108" s="66">
+      <c r="O108" s="63">
         <f t="shared" si="2"/>
         <v>22.66</v>
       </c>
@@ -7562,7 +7550,7 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="C109" s="61" t="s">
+      <c r="C109" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D109" s="38" t="s">
@@ -7592,13 +7580,13 @@
       <c r="L109" s="38">
         <v>11</v>
       </c>
-      <c r="M109" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N109" s="68">
+      <c r="M109" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N109" s="65">
         <v>20.93</v>
       </c>
-      <c r="O109" s="68">
+      <c r="O109" s="65">
         <f t="shared" si="2"/>
         <v>230.23</v>
       </c>
@@ -7610,7 +7598,7 @@
         <f>ROW(B110) - ROW($B$9)</f>
         <v>101</v>
       </c>
-      <c r="C110" s="60" t="s">
+      <c r="C110" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D110" s="36" t="s">
@@ -7640,13 +7628,13 @@
       <c r="L110" s="36">
         <v>25</v>
       </c>
-      <c r="M110" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N110" s="66">
+      <c r="M110" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N110" s="63">
         <v>0.2409</v>
       </c>
-      <c r="O110" s="66">
+      <c r="O110" s="63">
         <f t="shared" si="2"/>
         <v>6.0225</v>
       </c>
@@ -7658,7 +7646,7 @@
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="C111" s="61" t="s">
+      <c r="C111" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D111" s="38" t="s">
@@ -7688,13 +7676,13 @@
       <c r="L111" s="38">
         <v>11</v>
       </c>
-      <c r="M111" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N111" s="68">
+      <c r="M111" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N111" s="65">
         <v>0.96409999999999996</v>
       </c>
-      <c r="O111" s="68">
+      <c r="O111" s="65">
         <f t="shared" si="2"/>
         <v>10.6051</v>
       </c>
@@ -7706,7 +7694,7 @@
         <f>ROW(B112) - ROW($B$9)</f>
         <v>103</v>
       </c>
-      <c r="C112" s="60" t="s">
+      <c r="C112" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D112" s="36" t="s">
@@ -7736,13 +7724,13 @@
       <c r="L112" s="36">
         <v>11</v>
       </c>
-      <c r="M112" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N112" s="66">
+      <c r="M112" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N112" s="63">
         <v>6.3104999999999993</v>
       </c>
-      <c r="O112" s="66">
+      <c r="O112" s="63">
         <f t="shared" si="2"/>
         <v>69.415499999999994</v>
       </c>
@@ -7754,7 +7742,7 @@
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="C113" s="61" t="s">
+      <c r="C113" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D113" s="38" t="s">
@@ -7784,13 +7772,13 @@
       <c r="L113" s="38">
         <v>11</v>
       </c>
-      <c r="M113" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N113" s="68">
+      <c r="M113" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N113" s="65">
         <v>14.936</v>
       </c>
-      <c r="O113" s="68">
+      <c r="O113" s="65">
         <f t="shared" si="2"/>
         <v>164.29599999999999</v>
       </c>
@@ -7802,7 +7790,7 @@
         <f>ROW(B114) - ROW($B$9)</f>
         <v>105</v>
       </c>
-      <c r="C114" s="60" t="s">
+      <c r="C114" s="57" t="s">
         <v>486</v>
       </c>
       <c r="D114" s="36" t="s">
@@ -7832,13 +7820,13 @@
       <c r="L114" s="36">
         <v>11</v>
       </c>
-      <c r="M114" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N114" s="66">
+      <c r="M114" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N114" s="63">
         <v>13.7875</v>
       </c>
-      <c r="O114" s="66">
+      <c r="O114" s="63">
         <f t="shared" si="2"/>
         <v>151.66249999999999</v>
       </c>
@@ -7850,7 +7838,7 @@
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="C115" s="61" t="s">
+      <c r="C115" s="58" t="s">
         <v>486</v>
       </c>
       <c r="D115" s="38" t="s">
@@ -7880,13 +7868,13 @@
       <c r="L115" s="38">
         <v>11</v>
       </c>
-      <c r="M115" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N115" s="68">
+      <c r="M115" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N115" s="65">
         <v>17.600000000000001</v>
       </c>
-      <c r="O115" s="68">
+      <c r="O115" s="65">
         <f t="shared" si="2"/>
         <v>193.60000000000002</v>
       </c>
@@ -7898,7 +7886,7 @@
         <f>ROW(B116) - ROW($B$9)</f>
         <v>107</v>
       </c>
-      <c r="C116" s="60" t="s">
+      <c r="C116" s="57" t="s">
         <v>492</v>
       </c>
       <c r="D116" s="36" t="s">
@@ -7928,13 +7916,13 @@
       <c r="L116" s="36">
         <v>22</v>
       </c>
-      <c r="M116" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N116" s="66">
+      <c r="M116" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N116" s="63">
         <v>0.44950000000000001</v>
       </c>
-      <c r="O116" s="66">
+      <c r="O116" s="63">
         <f t="shared" si="2"/>
         <v>9.8889999999999993</v>
       </c>
@@ -7946,7 +7934,7 @@
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="C117" s="61" t="s">
+      <c r="C117" s="58" t="s">
         <v>492</v>
       </c>
       <c r="D117" s="38" t="s">
@@ -7976,13 +7964,13 @@
       <c r="L117" s="38">
         <v>15</v>
       </c>
-      <c r="M117" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N117" s="68">
+      <c r="M117" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N117" s="65">
         <v>0.1865</v>
       </c>
-      <c r="O117" s="68">
+      <c r="O117" s="65">
         <f t="shared" si="2"/>
         <v>2.7974999999999999</v>
       </c>
@@ -7994,7 +7982,7 @@
         <f>ROW(B118) - ROW($B$9)</f>
         <v>109</v>
       </c>
-      <c r="C118" s="60" t="s">
+      <c r="C118" s="57" t="s">
         <v>492</v>
       </c>
       <c r="D118" s="36" t="s">
@@ -8024,13 +8012,13 @@
       <c r="L118" s="36">
         <v>11</v>
       </c>
-      <c r="M118" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="N118" s="66">
+      <c r="M118" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="N118" s="63">
         <v>0.26180000000000003</v>
       </c>
-      <c r="O118" s="66">
+      <c r="O118" s="63">
         <f t="shared" si="2"/>
         <v>2.8798000000000004</v>
       </c>
@@ -8042,7 +8030,7 @@
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="C119" s="61" t="s">
+      <c r="C119" s="58" t="s">
         <v>492</v>
       </c>
       <c r="D119" s="38" t="s">
@@ -8072,13 +8060,13 @@
       <c r="L119" s="38">
         <v>11</v>
       </c>
-      <c r="M119" s="67" t="s">
-        <v>514</v>
-      </c>
-      <c r="N119" s="68">
+      <c r="M119" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="N119" s="65">
         <v>0.34360000000000002</v>
       </c>
-      <c r="O119" s="68">
+      <c r="O119" s="65">
         <f t="shared" si="2"/>
         <v>3.7796000000000003</v>
       </c>
@@ -8096,14 +8084,14 @@
       <c r="I120" s="34"/>
       <c r="J120" s="35"/>
       <c r="K120" s="35"/>
-      <c r="L120" s="71" t="s">
+      <c r="L120" s="73" t="s">
         <v>510</v>
       </c>
-      <c r="M120" s="72"/>
-      <c r="N120" s="72"/>
-      <c r="O120" s="69">
+      <c r="M120" s="74"/>
+      <c r="N120" s="74"/>
+      <c r="O120" s="66">
         <f>SUM(O10:O119)</f>
-        <v>1784.3428999999996</v>
+        <v>1787.6428999999998</v>
       </c>
       <c r="P120" s="41"/>
     </row>
@@ -8119,14 +8107,14 @@
       <c r="I121" s="9"/>
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
-      <c r="L121" s="71" t="s">
+      <c r="L121" s="73" t="s">
         <v>511</v>
       </c>
-      <c r="M121" s="72"/>
-      <c r="N121" s="72"/>
-      <c r="O121" s="70">
+      <c r="M121" s="74"/>
+      <c r="N121" s="74"/>
+      <c r="O121" s="67">
         <f>O120/10</f>
-        <v>178.43428999999998</v>
+        <v>178.76428999999999</v>
       </c>
       <c r="P121" s="42"/>
     </row>
@@ -8141,2887 +8129,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03143749-54F5-4014-A7EC-363C343FA80C}">
-  <dimension ref="A1:K113"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>509</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>507</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="36">
-        <v>12</v>
-      </c>
-      <c r="B3" s="66">
-        <v>0.1178</v>
-      </c>
-      <c r="C3" s="66">
-        <f>B3*A3</f>
-        <v>1.4136</v>
-      </c>
-      <c r="E3" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F3" s="77">
-        <f>E3+B3</f>
-        <v>0.21779999999999999</v>
-      </c>
-      <c r="H3" s="79">
-        <f>F3*A3</f>
-        <v>2.6135999999999999</v>
-      </c>
-      <c r="K3">
-        <v>0.21779999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="38">
-        <v>15</v>
-      </c>
-      <c r="B4" s="68">
-        <v>0.10349999999999999</v>
-      </c>
-      <c r="C4" s="66">
-        <f t="shared" ref="C4:C67" si="0">B4*A4</f>
-        <v>1.5525</v>
-      </c>
-      <c r="E4" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F4" s="77">
-        <f t="shared" ref="F4:F67" si="1">E4+B4</f>
-        <v>0.20350000000000001</v>
-      </c>
-      <c r="H4" s="79">
-        <f t="shared" ref="H4:H67" si="2">F4*A4</f>
-        <v>3.0525000000000002</v>
-      </c>
-      <c r="K4">
-        <v>0.20350000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="36">
-        <v>100</v>
-      </c>
-      <c r="B5" s="66">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="C5" s="66">
-        <f t="shared" si="0"/>
-        <v>0.21</v>
-      </c>
-      <c r="E5" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10210000000000001</v>
-      </c>
-      <c r="H5" s="79">
-        <f t="shared" si="2"/>
-        <v>10.210000000000001</v>
-      </c>
-      <c r="K5">
-        <v>0.10210000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="38">
-        <v>100</v>
-      </c>
-      <c r="B6" s="68">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C6" s="66">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="E6" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10300000000000001</v>
-      </c>
-      <c r="H6" s="79">
-        <f t="shared" si="2"/>
-        <v>10.3</v>
-      </c>
-      <c r="K6">
-        <v>0.10300000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="36">
-        <v>80</v>
-      </c>
-      <c r="B7" s="66">
-        <v>1.8100000000000002E-2</v>
-      </c>
-      <c r="C7" s="66">
-        <f t="shared" si="0"/>
-        <v>1.4480000000000002</v>
-      </c>
-      <c r="E7" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11810000000000001</v>
-      </c>
-      <c r="H7" s="79">
-        <f t="shared" si="2"/>
-        <v>9.4480000000000004</v>
-      </c>
-      <c r="K7">
-        <v>0.11810000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="38">
-        <v>1300</v>
-      </c>
-      <c r="B8" s="68">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C8" s="66">
-        <f t="shared" si="0"/>
-        <v>1.17</v>
-      </c>
-      <c r="E8" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1009</v>
-      </c>
-      <c r="H8" s="79">
-        <f t="shared" si="2"/>
-        <v>131.17000000000002</v>
-      </c>
-      <c r="K8">
-        <v>0.1009</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="36">
-        <v>180</v>
-      </c>
-      <c r="B9" s="66">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="C9" s="66">
-        <f t="shared" si="0"/>
-        <v>2.556</v>
-      </c>
-      <c r="E9" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11420000000000001</v>
-      </c>
-      <c r="H9" s="79">
-        <f t="shared" si="2"/>
-        <v>20.556000000000001</v>
-      </c>
-      <c r="K9">
-        <v>0.11420000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="38">
-        <v>280</v>
-      </c>
-      <c r="B10" s="68">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="C10" s="66">
-        <f t="shared" si="0"/>
-        <v>3.8079999999999998</v>
-      </c>
-      <c r="E10" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F10" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11360000000000001</v>
-      </c>
-      <c r="H10" s="79">
-        <f t="shared" si="2"/>
-        <v>31.808000000000003</v>
-      </c>
-      <c r="K10">
-        <v>0.11360000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="36">
-        <v>300</v>
-      </c>
-      <c r="B11" s="66">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="C11" s="66">
-        <f t="shared" si="0"/>
-        <v>1.5599999999999998</v>
-      </c>
-      <c r="E11" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F11" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1052</v>
-      </c>
-      <c r="H11" s="79">
-        <f t="shared" si="2"/>
-        <v>31.560000000000002</v>
-      </c>
-      <c r="K11">
-        <v>0.1052</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="38">
-        <v>100</v>
-      </c>
-      <c r="B12" s="68">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="C12" s="66">
-        <f t="shared" si="0"/>
-        <v>0.31</v>
-      </c>
-      <c r="E12" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F12" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10310000000000001</v>
-      </c>
-      <c r="H12" s="79">
-        <f t="shared" si="2"/>
-        <v>10.31</v>
-      </c>
-      <c r="K12">
-        <v>0.10310000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="36">
-        <v>50</v>
-      </c>
-      <c r="B13" s="66">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="C13" s="66">
-        <f t="shared" si="0"/>
-        <v>0.375</v>
-      </c>
-      <c r="E13" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F13" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10750000000000001</v>
-      </c>
-      <c r="H13" s="79">
-        <f t="shared" si="2"/>
-        <v>5.3750000000000009</v>
-      </c>
-      <c r="K13">
-        <v>0.10750000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="38">
-        <v>100</v>
-      </c>
-      <c r="B14" s="68">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="C14" s="66">
-        <f t="shared" si="0"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="E14" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F14" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10290000000000001</v>
-      </c>
-      <c r="H14" s="79">
-        <f t="shared" si="2"/>
-        <v>10.290000000000001</v>
-      </c>
-      <c r="K14">
-        <v>0.10290000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="36">
-        <v>50</v>
-      </c>
-      <c r="B15" s="66">
-        <v>1.3299999999999999E-2</v>
-      </c>
-      <c r="C15" s="66">
-        <f t="shared" si="0"/>
-        <v>0.66499999999999992</v>
-      </c>
-      <c r="E15" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11330000000000001</v>
-      </c>
-      <c r="H15" s="79">
-        <f t="shared" si="2"/>
-        <v>5.6650000000000009</v>
-      </c>
-      <c r="K15">
-        <v>0.11330000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="38">
-        <v>100</v>
-      </c>
-      <c r="B16" s="68">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="C16" s="66">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
-      </c>
-      <c r="E16" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1027</v>
-      </c>
-      <c r="H16" s="79">
-        <f t="shared" si="2"/>
-        <v>10.27</v>
-      </c>
-      <c r="K16">
-        <v>0.1027</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="36">
-        <v>50</v>
-      </c>
-      <c r="B17" s="66">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="C17" s="66">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="E17" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F17" s="77">
-        <f t="shared" si="1"/>
-        <v>0.115</v>
-      </c>
-      <c r="H17" s="79">
-        <f t="shared" si="2"/>
-        <v>5.75</v>
-      </c>
-      <c r="K17">
-        <v>0.115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="38">
-        <v>150</v>
-      </c>
-      <c r="B18" s="68">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="C18" s="66">
-        <f t="shared" si="0"/>
-        <v>1.05</v>
-      </c>
-      <c r="E18" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10700000000000001</v>
-      </c>
-      <c r="H18" s="79">
-        <f t="shared" si="2"/>
-        <v>16.05</v>
-      </c>
-      <c r="K18">
-        <v>0.10700000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="36">
-        <v>100</v>
-      </c>
-      <c r="B19" s="66">
-        <v>2.8E-3</v>
-      </c>
-      <c r="C19" s="66">
-        <f t="shared" si="0"/>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="E19" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1028</v>
-      </c>
-      <c r="H19" s="79">
-        <f t="shared" si="2"/>
-        <v>10.280000000000001</v>
-      </c>
-      <c r="K19">
-        <v>0.1028</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="38">
-        <v>100</v>
-      </c>
-      <c r="B20" s="68">
-        <v>2.0199999999999999E-2</v>
-      </c>
-      <c r="C20" s="66">
-        <f t="shared" si="0"/>
-        <v>2.02</v>
-      </c>
-      <c r="E20" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F20" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1202</v>
-      </c>
-      <c r="H20" s="79">
-        <f t="shared" si="2"/>
-        <v>12.02</v>
-      </c>
-      <c r="K20">
-        <v>0.1202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="36">
-        <v>100</v>
-      </c>
-      <c r="B21" s="66">
-        <v>1.95E-2</v>
-      </c>
-      <c r="C21" s="66">
-        <f t="shared" si="0"/>
-        <v>1.95</v>
-      </c>
-      <c r="E21" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11950000000000001</v>
-      </c>
-      <c r="H21" s="79">
-        <f t="shared" si="2"/>
-        <v>11.950000000000001</v>
-      </c>
-      <c r="K21">
-        <v>0.11950000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="38">
-        <v>40</v>
-      </c>
-      <c r="B22" s="68">
-        <v>4.7699999999999999E-2</v>
-      </c>
-      <c r="C22" s="66">
-        <f t="shared" si="0"/>
-        <v>1.9079999999999999</v>
-      </c>
-      <c r="E22" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F22" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1477</v>
-      </c>
-      <c r="H22" s="79">
-        <f t="shared" si="2"/>
-        <v>5.9079999999999995</v>
-      </c>
-      <c r="K22">
-        <v>0.1477</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="36">
-        <v>100</v>
-      </c>
-      <c r="B23" s="66">
-        <v>2.92E-2</v>
-      </c>
-      <c r="C23" s="66">
-        <f t="shared" si="0"/>
-        <v>2.92</v>
-      </c>
-      <c r="E23" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F23" s="77">
-        <f t="shared" si="1"/>
-        <v>0.12920000000000001</v>
-      </c>
-      <c r="H23" s="79">
-        <f t="shared" si="2"/>
-        <v>12.920000000000002</v>
-      </c>
-      <c r="K23">
-        <v>0.12920000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="38">
-        <v>55</v>
-      </c>
-      <c r="B24" s="68">
-        <v>0.11609999999999999</v>
-      </c>
-      <c r="C24" s="66">
-        <f t="shared" si="0"/>
-        <v>6.3854999999999995</v>
-      </c>
-      <c r="E24" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="77">
-        <f t="shared" si="1"/>
-        <v>0.21610000000000001</v>
-      </c>
-      <c r="H24" s="79">
-        <f t="shared" si="2"/>
-        <v>11.8855</v>
-      </c>
-      <c r="K24">
-        <v>0.21610000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="36">
-        <v>35</v>
-      </c>
-      <c r="B25" s="66">
-        <v>8.3599999999999994E-2</v>
-      </c>
-      <c r="C25" s="66">
-        <f t="shared" si="0"/>
-        <v>2.9259999999999997</v>
-      </c>
-      <c r="E25" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="77">
-        <f t="shared" si="1"/>
-        <v>0.18359999999999999</v>
-      </c>
-      <c r="H25" s="79">
-        <f t="shared" si="2"/>
-        <v>6.4259999999999993</v>
-      </c>
-      <c r="K25">
-        <v>0.18359999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="38">
-        <v>12</v>
-      </c>
-      <c r="B26" s="68">
-        <v>0.31850000000000001</v>
-      </c>
-      <c r="C26" s="66">
-        <f t="shared" si="0"/>
-        <v>3.8220000000000001</v>
-      </c>
-      <c r="E26" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F26" s="77">
-        <f t="shared" si="1"/>
-        <v>0.41849999999999998</v>
-      </c>
-      <c r="H26" s="79">
-        <f t="shared" si="2"/>
-        <v>5.0220000000000002</v>
-      </c>
-      <c r="K26">
-        <v>0.41849999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="36">
-        <v>20</v>
-      </c>
-      <c r="B27" s="66">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="C27" s="66">
-        <f t="shared" si="0"/>
-        <v>0.72400000000000009</v>
-      </c>
-      <c r="E27" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13620000000000002</v>
-      </c>
-      <c r="H27" s="79">
-        <f t="shared" si="2"/>
-        <v>2.7240000000000002</v>
-      </c>
-      <c r="K27">
-        <v>0.13620000000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="38">
-        <v>20</v>
-      </c>
-      <c r="B28" s="68">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="C28" s="66">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
-      </c>
-      <c r="E28" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F28" s="77">
-        <f t="shared" si="1"/>
-        <v>0.14900000000000002</v>
-      </c>
-      <c r="H28" s="79">
-        <f t="shared" si="2"/>
-        <v>2.9800000000000004</v>
-      </c>
-      <c r="K28">
-        <v>0.14900000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="36">
-        <v>20</v>
-      </c>
-      <c r="B29" s="66">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="C29" s="66">
-        <f t="shared" si="0"/>
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="E29" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F29" s="77">
-        <f t="shared" si="1"/>
-        <v>0.12820000000000001</v>
-      </c>
-      <c r="H29" s="79">
-        <f t="shared" si="2"/>
-        <v>2.5640000000000001</v>
-      </c>
-      <c r="K29">
-        <v>0.12820000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="38">
-        <v>12</v>
-      </c>
-      <c r="B30" s="68">
-        <v>0.57669999999999999</v>
-      </c>
-      <c r="C30" s="66">
-        <f t="shared" si="0"/>
-        <v>6.9203999999999999</v>
-      </c>
-      <c r="E30" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="77">
-        <f t="shared" si="1"/>
-        <v>0.67669999999999997</v>
-      </c>
-      <c r="H30" s="79">
-        <f t="shared" si="2"/>
-        <v>8.1204000000000001</v>
-      </c>
-      <c r="K30">
-        <v>0.67669999999999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="36">
-        <v>11</v>
-      </c>
-      <c r="B31" s="66">
-        <v>0.13469999999999999</v>
-      </c>
-      <c r="C31" s="66">
-        <f t="shared" si="0"/>
-        <v>1.4816999999999998</v>
-      </c>
-      <c r="E31" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F31" s="77">
-        <f t="shared" si="1"/>
-        <v>0.23469999999999999</v>
-      </c>
-      <c r="H31" s="79">
-        <f t="shared" si="2"/>
-        <v>2.5817000000000001</v>
-      </c>
-      <c r="K31">
-        <v>0.23469999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="38">
-        <v>12</v>
-      </c>
-      <c r="B32" s="68">
-        <v>0.13569999999999999</v>
-      </c>
-      <c r="C32" s="66">
-        <f t="shared" si="0"/>
-        <v>1.6283999999999998</v>
-      </c>
-      <c r="E32" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F32" s="77">
-        <f t="shared" si="1"/>
-        <v>0.23569999999999999</v>
-      </c>
-      <c r="H32" s="79">
-        <f t="shared" si="2"/>
-        <v>2.8283999999999998</v>
-      </c>
-      <c r="K32">
-        <v>0.23569999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="36">
-        <v>11</v>
-      </c>
-      <c r="B33" s="66">
-        <v>1.7351000000000001</v>
-      </c>
-      <c r="C33" s="66">
-        <f t="shared" si="0"/>
-        <v>19.086100000000002</v>
-      </c>
-      <c r="E33" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F33" s="77">
-        <f t="shared" si="1"/>
-        <v>1.8351000000000002</v>
-      </c>
-      <c r="H33" s="79">
-        <f t="shared" si="2"/>
-        <v>20.186100000000003</v>
-      </c>
-      <c r="K33">
-        <v>1.8351000000000002</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="38">
-        <v>12</v>
-      </c>
-      <c r="B34" s="68">
-        <v>0.42870000000000003</v>
-      </c>
-      <c r="C34" s="66">
-        <f t="shared" si="0"/>
-        <v>5.1444000000000001</v>
-      </c>
-      <c r="E34" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F34" s="77">
-        <f t="shared" si="1"/>
-        <v>0.52870000000000006</v>
-      </c>
-      <c r="H34" s="79">
-        <f t="shared" si="2"/>
-        <v>6.3444000000000003</v>
-      </c>
-      <c r="K34">
-        <v>0.52870000000000006</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="36">
-        <v>25</v>
-      </c>
-      <c r="B35" s="66">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="C35" s="66">
-        <f t="shared" si="0"/>
-        <v>2.1875</v>
-      </c>
-      <c r="E35" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F35" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1875</v>
-      </c>
-      <c r="H35" s="79">
-        <f t="shared" si="2"/>
-        <v>4.6875</v>
-      </c>
-      <c r="K35">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="38">
-        <v>20</v>
-      </c>
-      <c r="B36" s="68">
-        <v>4.4699999999999997E-2</v>
-      </c>
-      <c r="C36" s="66">
-        <f t="shared" si="0"/>
-        <v>0.89399999999999991</v>
-      </c>
-      <c r="E36" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F36" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1447</v>
-      </c>
-      <c r="H36" s="79">
-        <f t="shared" si="2"/>
-        <v>2.8940000000000001</v>
-      </c>
-      <c r="K36">
-        <v>0.1447</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="36">
-        <v>12</v>
-      </c>
-      <c r="B37" s="66">
-        <v>0.30130000000000001</v>
-      </c>
-      <c r="C37" s="66">
-        <f t="shared" si="0"/>
-        <v>3.6156000000000001</v>
-      </c>
-      <c r="E37" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F37" s="77">
-        <f t="shared" si="1"/>
-        <v>0.40129999999999999</v>
-      </c>
-      <c r="H37" s="79">
-        <f t="shared" si="2"/>
-        <v>4.8155999999999999</v>
-      </c>
-      <c r="K37">
-        <v>0.40129999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="38">
-        <v>12</v>
-      </c>
-      <c r="B38" s="68">
-        <v>0.66449999999999998</v>
-      </c>
-      <c r="C38" s="66">
-        <f t="shared" si="0"/>
-        <v>7.9740000000000002</v>
-      </c>
-      <c r="E38" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F38" s="77">
-        <f t="shared" si="1"/>
-        <v>0.76449999999999996</v>
-      </c>
-      <c r="H38" s="79">
-        <f t="shared" si="2"/>
-        <v>9.1739999999999995</v>
-      </c>
-      <c r="K38">
-        <v>0.76449999999999996</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="36">
-        <v>12</v>
-      </c>
-      <c r="B39" s="66">
-        <v>0.1704</v>
-      </c>
-      <c r="C39" s="66">
-        <f t="shared" si="0"/>
-        <v>2.0448</v>
-      </c>
-      <c r="E39" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F39" s="77">
-        <f t="shared" si="1"/>
-        <v>0.27039999999999997</v>
-      </c>
-      <c r="H39" s="79">
-        <f t="shared" si="2"/>
-        <v>3.2447999999999997</v>
-      </c>
-      <c r="K39">
-        <v>0.27039999999999997</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="38">
-        <v>20</v>
-      </c>
-      <c r="B40" s="68">
-        <v>5.1499999999999997E-2</v>
-      </c>
-      <c r="C40" s="66">
-        <f t="shared" si="0"/>
-        <v>1.03</v>
-      </c>
-      <c r="E40" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F40" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1515</v>
-      </c>
-      <c r="H40" s="79">
-        <f t="shared" si="2"/>
-        <v>3.03</v>
-      </c>
-      <c r="K40">
-        <v>0.1515</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="36">
-        <v>30</v>
-      </c>
-      <c r="B41" s="66">
-        <v>6.0900000000000003E-2</v>
-      </c>
-      <c r="C41" s="66">
-        <f t="shared" si="0"/>
-        <v>1.8270000000000002</v>
-      </c>
-      <c r="E41" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F41" s="77">
-        <f t="shared" si="1"/>
-        <v>0.16090000000000002</v>
-      </c>
-      <c r="H41" s="79">
-        <f t="shared" si="2"/>
-        <v>4.8270000000000008</v>
-      </c>
-      <c r="K41">
-        <v>0.16090000000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="38">
-        <v>12</v>
-      </c>
-      <c r="B42" s="68">
-        <v>0.14030000000000001</v>
-      </c>
-      <c r="C42" s="66">
-        <f t="shared" si="0"/>
-        <v>1.6836000000000002</v>
-      </c>
-      <c r="E42" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F42" s="77">
-        <f t="shared" si="1"/>
-        <v>0.24030000000000001</v>
-      </c>
-      <c r="H42" s="79">
-        <f t="shared" si="2"/>
-        <v>2.8836000000000004</v>
-      </c>
-      <c r="K42">
-        <v>0.24030000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="36">
-        <v>30</v>
-      </c>
-      <c r="B43" s="66">
-        <v>4.3799999999999999E-2</v>
-      </c>
-      <c r="C43" s="66">
-        <f t="shared" si="0"/>
-        <v>1.3140000000000001</v>
-      </c>
-      <c r="E43" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F43" s="77">
-        <f t="shared" si="1"/>
-        <v>0.14380000000000001</v>
-      </c>
-      <c r="H43" s="79">
-        <f t="shared" si="2"/>
-        <v>4.3140000000000001</v>
-      </c>
-      <c r="K43">
-        <v>0.14380000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="38">
-        <v>22</v>
-      </c>
-      <c r="B44" s="68">
-        <v>0.13650000000000001</v>
-      </c>
-      <c r="C44" s="66">
-        <f t="shared" si="0"/>
-        <v>3.0030000000000001</v>
-      </c>
-      <c r="E44" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F44" s="77">
-        <f t="shared" si="1"/>
-        <v>0.23650000000000002</v>
-      </c>
-      <c r="H44" s="79">
-        <f t="shared" si="2"/>
-        <v>5.2030000000000003</v>
-      </c>
-      <c r="K44">
-        <v>0.23650000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="36">
-        <v>22</v>
-      </c>
-      <c r="B45" s="66">
-        <v>0.14799999999999999</v>
-      </c>
-      <c r="C45" s="66">
-        <f t="shared" si="0"/>
-        <v>3.2559999999999998</v>
-      </c>
-      <c r="E45" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F45" s="77">
-        <f t="shared" si="1"/>
-        <v>0.248</v>
-      </c>
-      <c r="H45" s="79">
-        <f t="shared" si="2"/>
-        <v>5.4559999999999995</v>
-      </c>
-      <c r="K45">
-        <v>0.248</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="38">
-        <v>20</v>
-      </c>
-      <c r="B46" s="68">
-        <v>7.0599999999999996E-2</v>
-      </c>
-      <c r="C46" s="66">
-        <f t="shared" si="0"/>
-        <v>1.4119999999999999</v>
-      </c>
-      <c r="E46" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1706</v>
-      </c>
-      <c r="H46" s="79">
-        <f t="shared" si="2"/>
-        <v>3.4119999999999999</v>
-      </c>
-      <c r="K46">
-        <v>0.1706</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="36">
-        <v>100</v>
-      </c>
-      <c r="B47" s="66">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="C47" s="66">
-        <f t="shared" si="0"/>
-        <v>0.31</v>
-      </c>
-      <c r="E47" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F47" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10310000000000001</v>
-      </c>
-      <c r="H47" s="79">
-        <f t="shared" si="2"/>
-        <v>10.31</v>
-      </c>
-      <c r="K47">
-        <v>0.10310000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="38">
-        <v>20</v>
-      </c>
-      <c r="B48" s="68">
-        <v>5.62E-2</v>
-      </c>
-      <c r="C48" s="66">
-        <f t="shared" si="0"/>
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="E48" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F48" s="77">
-        <f t="shared" si="1"/>
-        <v>0.15620000000000001</v>
-      </c>
-      <c r="H48" s="79">
-        <f t="shared" si="2"/>
-        <v>3.1240000000000001</v>
-      </c>
-      <c r="K48">
-        <v>0.15620000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="36">
-        <v>50</v>
-      </c>
-      <c r="B49" s="66">
-        <v>1.6299999999999999E-2</v>
-      </c>
-      <c r="C49" s="66">
-        <f t="shared" si="0"/>
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="E49" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F49" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1163</v>
-      </c>
-      <c r="H49" s="79">
-        <f t="shared" si="2"/>
-        <v>5.8150000000000004</v>
-      </c>
-      <c r="K49">
-        <v>0.1163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="38">
-        <v>20</v>
-      </c>
-      <c r="B50" s="68">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="C50" s="66">
-        <f t="shared" si="0"/>
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="E50" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F50" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13540000000000002</v>
-      </c>
-      <c r="H50" s="79">
-        <f t="shared" si="2"/>
-        <v>2.7080000000000002</v>
-      </c>
-      <c r="K50">
-        <v>0.13540000000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="36">
-        <v>20</v>
-      </c>
-      <c r="B51" s="66">
-        <v>3.5200000000000002E-2</v>
-      </c>
-      <c r="C51" s="66">
-        <f t="shared" si="0"/>
-        <v>0.70400000000000007</v>
-      </c>
-      <c r="E51" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F51" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13520000000000001</v>
-      </c>
-      <c r="H51" s="79">
-        <f t="shared" si="2"/>
-        <v>2.7040000000000002</v>
-      </c>
-      <c r="K51">
-        <v>0.13520000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="38">
-        <v>50</v>
-      </c>
-      <c r="B52" s="68">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="C52" s="66">
-        <f t="shared" si="0"/>
-        <v>0.79500000000000004</v>
-      </c>
-      <c r="E52" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F52" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1159</v>
-      </c>
-      <c r="H52" s="79">
-        <f t="shared" si="2"/>
-        <v>5.7949999999999999</v>
-      </c>
-      <c r="K52">
-        <v>0.1159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="36" t="s">
-        <v>480</v>
-      </c>
-      <c r="B53" s="66" t="s">
-        <v>480</v>
-      </c>
-      <c r="C53" s="66">
-        <v>0</v>
-      </c>
-      <c r="E53" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F53" s="77">
-        <v>0</v>
-      </c>
-      <c r="H53" s="79">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="38">
-        <v>150</v>
-      </c>
-      <c r="B54" s="68">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="C54" s="66">
-        <f t="shared" si="0"/>
-        <v>2.04</v>
-      </c>
-      <c r="E54" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F54" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11360000000000001</v>
-      </c>
-      <c r="H54" s="79">
-        <f t="shared" si="2"/>
-        <v>17.040000000000003</v>
-      </c>
-      <c r="K54">
-        <v>0.11360000000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="36">
-        <v>20</v>
-      </c>
-      <c r="B55" s="66">
-        <v>3.15E-2</v>
-      </c>
-      <c r="C55" s="66">
-        <f t="shared" si="0"/>
-        <v>0.63</v>
-      </c>
-      <c r="E55" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F55" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13150000000000001</v>
-      </c>
-      <c r="H55" s="79">
-        <f t="shared" si="2"/>
-        <v>2.63</v>
-      </c>
-      <c r="K55">
-        <v>0.13150000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="38">
-        <v>50</v>
-      </c>
-      <c r="B56" s="68">
-        <v>1.6500000000000001E-2</v>
-      </c>
-      <c r="C56" s="66">
-        <f t="shared" si="0"/>
-        <v>0.82500000000000007</v>
-      </c>
-      <c r="E56" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F56" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11650000000000001</v>
-      </c>
-      <c r="H56" s="79">
-        <f t="shared" si="2"/>
-        <v>5.8250000000000002</v>
-      </c>
-      <c r="K56">
-        <v>0.11650000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="36">
-        <v>20</v>
-      </c>
-      <c r="B57" s="66">
-        <v>3.6700000000000003E-2</v>
-      </c>
-      <c r="C57" s="66">
-        <f t="shared" si="0"/>
-        <v>0.7340000000000001</v>
-      </c>
-      <c r="E57" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F57" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13670000000000002</v>
-      </c>
-      <c r="H57" s="79">
-        <f t="shared" si="2"/>
-        <v>2.7340000000000004</v>
-      </c>
-      <c r="K57">
-        <v>0.13670000000000002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="38">
-        <v>60</v>
-      </c>
-      <c r="B58" s="68">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="C58" s="66">
-        <f t="shared" si="0"/>
-        <v>1.23</v>
-      </c>
-      <c r="E58" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F58" s="77">
-        <f t="shared" si="1"/>
-        <v>0.12050000000000001</v>
-      </c>
-      <c r="H58" s="79">
-        <f t="shared" si="2"/>
-        <v>7.23</v>
-      </c>
-      <c r="K58">
-        <v>0.12050000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="36">
-        <v>40</v>
-      </c>
-      <c r="B59" s="66">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="C59" s="66">
-        <f t="shared" si="0"/>
-        <v>1.2559999999999998</v>
-      </c>
-      <c r="E59" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F59" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13140000000000002</v>
-      </c>
-      <c r="H59" s="79">
-        <f t="shared" si="2"/>
-        <v>5.2560000000000002</v>
-      </c>
-      <c r="K59">
-        <v>0.13140000000000002</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="38">
-        <v>20</v>
-      </c>
-      <c r="B60" s="68">
-        <v>4.9599999999999998E-2</v>
-      </c>
-      <c r="C60" s="66">
-        <f t="shared" si="0"/>
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="E60" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F60" s="77">
-        <f t="shared" si="1"/>
-        <v>0.14960000000000001</v>
-      </c>
-      <c r="H60" s="79">
-        <f t="shared" si="2"/>
-        <v>2.992</v>
-      </c>
-      <c r="K60">
-        <v>0.14960000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="36">
-        <v>400</v>
-      </c>
-      <c r="B61" s="66">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="C61" s="66">
-        <f t="shared" si="0"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="E61" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F61" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1017</v>
-      </c>
-      <c r="H61" s="79">
-        <f t="shared" si="2"/>
-        <v>40.68</v>
-      </c>
-      <c r="K61">
-        <v>0.1017</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="38">
-        <v>80</v>
-      </c>
-      <c r="B62" s="68">
-        <v>3.27E-2</v>
-      </c>
-      <c r="C62" s="66">
-        <f t="shared" si="0"/>
-        <v>2.6160000000000001</v>
-      </c>
-      <c r="E62" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F62" s="77">
-        <f t="shared" si="1"/>
-        <v>0.13270000000000001</v>
-      </c>
-      <c r="H62" s="79">
-        <f t="shared" si="2"/>
-        <v>10.616000000000001</v>
-      </c>
-      <c r="K62">
-        <v>0.13270000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="36">
-        <v>50</v>
-      </c>
-      <c r="B63" s="66">
-        <v>1.3299999999999999E-2</v>
-      </c>
-      <c r="C63" s="66">
-        <f t="shared" si="0"/>
-        <v>0.66499999999999992</v>
-      </c>
-      <c r="E63" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F63" s="77">
-        <f t="shared" si="1"/>
-        <v>0.11330000000000001</v>
-      </c>
-      <c r="H63" s="79">
-        <f t="shared" si="2"/>
-        <v>5.6650000000000009</v>
-      </c>
-      <c r="K63">
-        <v>0.11330000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="38">
-        <v>20</v>
-      </c>
-      <c r="B64" s="68">
-        <v>2.5899999999999999E-2</v>
-      </c>
-      <c r="C64" s="66">
-        <f t="shared" si="0"/>
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="E64" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F64" s="77">
-        <f t="shared" si="1"/>
-        <v>0.12590000000000001</v>
-      </c>
-      <c r="H64" s="79">
-        <f t="shared" si="2"/>
-        <v>2.5180000000000002</v>
-      </c>
-      <c r="K64">
-        <v>0.12590000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="36">
-        <v>20</v>
-      </c>
-      <c r="B65" s="66">
-        <v>2.86E-2</v>
-      </c>
-      <c r="C65" s="66">
-        <f t="shared" si="0"/>
-        <v>0.57200000000000006</v>
-      </c>
-      <c r="E65" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F65" s="77">
-        <f t="shared" si="1"/>
-        <v>0.12859999999999999</v>
-      </c>
-      <c r="H65" s="79">
-        <f t="shared" si="2"/>
-        <v>2.5720000000000001</v>
-      </c>
-      <c r="K65">
-        <v>0.12859999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="38">
-        <v>100</v>
-      </c>
-      <c r="B66" s="68">
-        <v>1.4E-3</v>
-      </c>
-      <c r="C66" s="66">
-        <f t="shared" si="0"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="E66" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F66" s="77">
-        <f t="shared" si="1"/>
-        <v>0.1014</v>
-      </c>
-      <c r="H66" s="79">
-        <f t="shared" si="2"/>
-        <v>10.14</v>
-      </c>
-      <c r="K66">
-        <v>0.1014</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="36">
-        <v>100</v>
-      </c>
-      <c r="B67" s="66">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="C67" s="66">
-        <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-      <c r="E67" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F67" s="77">
-        <f t="shared" si="1"/>
-        <v>0.10120000000000001</v>
-      </c>
-      <c r="H67" s="79">
-        <f t="shared" si="2"/>
-        <v>10.120000000000001</v>
-      </c>
-      <c r="K67">
-        <v>0.10120000000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="38">
-        <v>100</v>
-      </c>
-      <c r="B68" s="68">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="C68" s="66">
-        <f t="shared" ref="C68:C112" si="3">B68*A68</f>
-        <v>0.11</v>
-      </c>
-      <c r="E68" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F68" s="77">
-        <f t="shared" ref="F68:F112" si="4">E68+B68</f>
-        <v>0.10110000000000001</v>
-      </c>
-      <c r="H68" s="79">
-        <f t="shared" ref="H68:H112" si="5">F68*A68</f>
-        <v>10.110000000000001</v>
-      </c>
-      <c r="K68">
-        <v>0.10110000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="36">
-        <v>20</v>
-      </c>
-      <c r="B69" s="66">
-        <v>2.5899999999999999E-2</v>
-      </c>
-      <c r="C69" s="66">
-        <f t="shared" si="3"/>
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="E69" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F69" s="77">
-        <f t="shared" si="4"/>
-        <v>0.12590000000000001</v>
-      </c>
-      <c r="H69" s="79">
-        <f t="shared" si="5"/>
-        <v>2.5180000000000002</v>
-      </c>
-      <c r="K69">
-        <v>0.12590000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="38">
-        <v>100</v>
-      </c>
-      <c r="B70" s="68">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="C70" s="66">
-        <f t="shared" si="3"/>
-        <v>0.13</v>
-      </c>
-      <c r="E70" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F70" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1013</v>
-      </c>
-      <c r="H70" s="79">
-        <f t="shared" si="5"/>
-        <v>10.130000000000001</v>
-      </c>
-      <c r="K70">
-        <v>0.1013</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="36">
-        <v>200</v>
-      </c>
-      <c r="B71" s="66">
-        <v>1E-3</v>
-      </c>
-      <c r="C71" s="66">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="E71" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F71" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="H71" s="79">
-        <f t="shared" si="5"/>
-        <v>20.200000000000003</v>
-      </c>
-      <c r="K71">
-        <v>0.10100000000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="38">
-        <v>100</v>
-      </c>
-      <c r="B72" s="68">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="C72" s="66">
-        <f t="shared" si="3"/>
-        <v>0.31</v>
-      </c>
-      <c r="E72" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F72" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10310000000000001</v>
-      </c>
-      <c r="H72" s="79">
-        <f t="shared" si="5"/>
-        <v>10.31</v>
-      </c>
-      <c r="K72">
-        <v>0.10310000000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="36">
-        <v>100</v>
-      </c>
-      <c r="B73" s="66">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C73" s="66">
-        <f t="shared" si="3"/>
-        <v>0.09</v>
-      </c>
-      <c r="E73" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F73" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1009</v>
-      </c>
-      <c r="H73" s="79">
-        <f t="shared" si="5"/>
-        <v>10.09</v>
-      </c>
-      <c r="K73">
-        <v>0.1009</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="38">
-        <v>20</v>
-      </c>
-      <c r="B74" s="68">
-        <v>1.9400000000000001E-2</v>
-      </c>
-      <c r="C74" s="66">
-        <f t="shared" si="3"/>
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="E74" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F74" s="77">
-        <f t="shared" si="4"/>
-        <v>0.11940000000000001</v>
-      </c>
-      <c r="H74" s="79">
-        <f t="shared" si="5"/>
-        <v>2.3879999999999999</v>
-      </c>
-      <c r="K74">
-        <v>0.11940000000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="36">
-        <v>100</v>
-      </c>
-      <c r="B75" s="66">
-        <v>2E-3</v>
-      </c>
-      <c r="C75" s="66">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="E75" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F75" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10200000000000001</v>
-      </c>
-      <c r="H75" s="79">
-        <f t="shared" si="5"/>
-        <v>10.200000000000001</v>
-      </c>
-      <c r="K75">
-        <v>0.10200000000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="38">
-        <v>200</v>
-      </c>
-      <c r="B76" s="68">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="C76" s="66">
-        <f t="shared" si="3"/>
-        <v>0.16</v>
-      </c>
-      <c r="E76" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F76" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1008</v>
-      </c>
-      <c r="H76" s="79">
-        <f t="shared" si="5"/>
-        <v>20.16</v>
-      </c>
-      <c r="K76">
-        <v>0.1008</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="36">
-        <v>50</v>
-      </c>
-      <c r="B77" s="66">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="C77" s="66">
-        <f t="shared" si="3"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="E77" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F77" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10680000000000001</v>
-      </c>
-      <c r="H77" s="79">
-        <f t="shared" si="5"/>
-        <v>5.34</v>
-      </c>
-      <c r="K77">
-        <v>0.10680000000000001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="38">
-        <v>100</v>
-      </c>
-      <c r="B78" s="68">
-        <v>1.43E-2</v>
-      </c>
-      <c r="C78" s="66">
-        <f t="shared" si="3"/>
-        <v>1.43</v>
-      </c>
-      <c r="E78" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F78" s="77">
-        <f t="shared" si="4"/>
-        <v>0.11430000000000001</v>
-      </c>
-      <c r="H78" s="79">
-        <f t="shared" si="5"/>
-        <v>11.430000000000001</v>
-      </c>
-      <c r="K78">
-        <v>0.11430000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="36">
-        <v>100</v>
-      </c>
-      <c r="B79" s="66">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C79" s="66">
-        <f t="shared" si="3"/>
-        <v>0.3</v>
-      </c>
-      <c r="E79" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F79" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10300000000000001</v>
-      </c>
-      <c r="H79" s="79">
-        <f t="shared" si="5"/>
-        <v>10.3</v>
-      </c>
-      <c r="K79">
-        <v>0.10300000000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="38">
-        <v>40</v>
-      </c>
-      <c r="B80" s="68">
-        <v>2.5700000000000001E-2</v>
-      </c>
-      <c r="C80" s="66">
-        <f t="shared" si="3"/>
-        <v>1.028</v>
-      </c>
-      <c r="E80" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F80" s="77">
-        <f t="shared" si="4"/>
-        <v>0.12570000000000001</v>
-      </c>
-      <c r="H80" s="79">
-        <f t="shared" si="5"/>
-        <v>5.0280000000000005</v>
-      </c>
-      <c r="K80">
-        <v>0.12570000000000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="36">
-        <v>100</v>
-      </c>
-      <c r="B81" s="66">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C81" s="66">
-        <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="E81" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F81" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10400000000000001</v>
-      </c>
-      <c r="H81" s="79">
-        <f t="shared" si="5"/>
-        <v>10.4</v>
-      </c>
-      <c r="K81">
-        <v>0.10400000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="38">
-        <v>100</v>
-      </c>
-      <c r="B82" s="68">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="C82" s="66">
-        <f t="shared" si="3"/>
-        <v>0.11</v>
-      </c>
-      <c r="E82" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F82" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10110000000000001</v>
-      </c>
-      <c r="H82" s="79">
-        <f t="shared" si="5"/>
-        <v>10.110000000000001</v>
-      </c>
-      <c r="K82">
-        <v>0.10110000000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="36">
-        <v>100</v>
-      </c>
-      <c r="B83" s="66">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="C83" s="66">
-        <f t="shared" si="3"/>
-        <v>0.11</v>
-      </c>
-      <c r="E83" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F83" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10110000000000001</v>
-      </c>
-      <c r="H83" s="79">
-        <f t="shared" si="5"/>
-        <v>10.110000000000001</v>
-      </c>
-      <c r="K83">
-        <v>0.10110000000000001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="38">
-        <v>100</v>
-      </c>
-      <c r="B84" s="68">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="C84" s="66">
-        <f t="shared" si="3"/>
-        <v>0.13</v>
-      </c>
-      <c r="E84" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F84" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1013</v>
-      </c>
-      <c r="H84" s="79">
-        <f t="shared" si="5"/>
-        <v>10.130000000000001</v>
-      </c>
-      <c r="K84">
-        <v>0.1013</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="36">
-        <v>100</v>
-      </c>
-      <c r="B85" s="66">
-        <v>1.4E-3</v>
-      </c>
-      <c r="C85" s="66">
-        <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="E85" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F85" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1014</v>
-      </c>
-      <c r="H85" s="79">
-        <f t="shared" si="5"/>
-        <v>10.14</v>
-      </c>
-      <c r="K85">
-        <v>0.1014</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="38">
-        <v>100</v>
-      </c>
-      <c r="B86" s="68">
-        <v>1.4E-3</v>
-      </c>
-      <c r="C86" s="66">
-        <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="E86" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F86" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1014</v>
-      </c>
-      <c r="H86" s="79">
-        <f t="shared" si="5"/>
-        <v>10.14</v>
-      </c>
-      <c r="K86">
-        <v>0.1014</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="36">
-        <v>100</v>
-      </c>
-      <c r="B87" s="66">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="C87" s="66">
-        <f t="shared" si="3"/>
-        <v>0.12</v>
-      </c>
-      <c r="E87" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F87" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10120000000000001</v>
-      </c>
-      <c r="H87" s="79">
-        <f t="shared" si="5"/>
-        <v>10.120000000000001</v>
-      </c>
-      <c r="K87">
-        <v>0.10120000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="38">
-        <v>45</v>
-      </c>
-      <c r="B88" s="68">
-        <v>8.5500000000000007E-2</v>
-      </c>
-      <c r="C88" s="66">
-        <f t="shared" si="3"/>
-        <v>3.8475000000000001</v>
-      </c>
-      <c r="E88" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F88" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1855</v>
-      </c>
-      <c r="H88" s="79">
-        <f t="shared" si="5"/>
-        <v>8.3475000000000001</v>
-      </c>
-      <c r="K88">
-        <v>0.1855</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="36">
-        <v>50</v>
-      </c>
-      <c r="B89" s="66">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="C89" s="66">
-        <f t="shared" si="3"/>
-        <v>0.245</v>
-      </c>
-      <c r="E89" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F89" s="77">
-        <f t="shared" si="4"/>
-        <v>0.10490000000000001</v>
-      </c>
-      <c r="H89" s="79">
-        <f t="shared" si="5"/>
-        <v>5.2450000000000001</v>
-      </c>
-      <c r="K89">
-        <v>0.10490000000000001</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="38">
-        <v>100</v>
-      </c>
-      <c r="B90" s="68">
-        <v>1.4E-3</v>
-      </c>
-      <c r="C90" s="66">
-        <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="E90" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F90" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1014</v>
-      </c>
-      <c r="H90" s="79">
-        <f t="shared" si="5"/>
-        <v>10.14</v>
-      </c>
-      <c r="K90">
-        <v>0.1014</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="36">
-        <v>20</v>
-      </c>
-      <c r="B91" s="66">
-        <v>3.61E-2</v>
-      </c>
-      <c r="C91" s="66">
-        <f t="shared" si="3"/>
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="E91" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F91" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1361</v>
-      </c>
-      <c r="H91" s="79">
-        <f t="shared" si="5"/>
-        <v>2.722</v>
-      </c>
-      <c r="K91">
-        <v>0.1361</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="38" t="s">
-        <v>480</v>
-      </c>
-      <c r="B92" s="68" t="s">
-        <v>480</v>
-      </c>
-      <c r="C92" s="66">
-        <v>0</v>
-      </c>
-      <c r="E92" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F92" s="77">
-        <v>0</v>
-      </c>
-      <c r="H92" s="79">
-        <v>0</v>
-      </c>
-      <c r="K92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="36">
-        <v>80</v>
-      </c>
-      <c r="B93" s="66">
-        <v>5.9499999999999997E-2</v>
-      </c>
-      <c r="C93" s="66">
-        <f t="shared" si="3"/>
-        <v>4.76</v>
-      </c>
-      <c r="E93" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F93" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1595</v>
-      </c>
-      <c r="H93" s="79">
-        <f t="shared" si="5"/>
-        <v>12.76</v>
-      </c>
-      <c r="K93">
-        <v>0.1595</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="74"/>
-      <c r="B94" s="76"/>
-      <c r="C94" s="66">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E94" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F94" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="H94" s="79">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K94">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="36">
-        <v>12</v>
-      </c>
-      <c r="B95" s="66">
-        <v>0.56289999999999996</v>
-      </c>
-      <c r="C95" s="66">
-        <f t="shared" si="3"/>
-        <v>6.7547999999999995</v>
-      </c>
-      <c r="E95" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F95" s="77">
-        <f t="shared" si="4"/>
-        <v>0.66289999999999993</v>
-      </c>
-      <c r="H95" s="79">
-        <f t="shared" si="5"/>
-        <v>7.9547999999999988</v>
-      </c>
-      <c r="K95">
-        <v>0.66289999999999993</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="38">
-        <v>22</v>
-      </c>
-      <c r="B96" s="68">
-        <v>0.15479999999999999</v>
-      </c>
-      <c r="C96" s="66">
-        <f t="shared" si="3"/>
-        <v>3.4055999999999997</v>
-      </c>
-      <c r="E96" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F96" s="77">
-        <f t="shared" si="4"/>
-        <v>0.25480000000000003</v>
-      </c>
-      <c r="H96" s="79">
-        <f t="shared" si="5"/>
-        <v>5.6056000000000008</v>
-      </c>
-      <c r="K96">
-        <v>0.25480000000000003</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="36">
-        <v>11</v>
-      </c>
-      <c r="B97" s="66">
-        <v>0.15559999999999999</v>
-      </c>
-      <c r="C97" s="66">
-        <f t="shared" si="3"/>
-        <v>1.7115999999999998</v>
-      </c>
-      <c r="E97" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F97" s="77">
-        <f t="shared" si="4"/>
-        <v>0.25559999999999999</v>
-      </c>
-      <c r="H97" s="79">
-        <f t="shared" si="5"/>
-        <v>2.8115999999999999</v>
-      </c>
-      <c r="K97">
-        <v>0.25559999999999999</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="38">
-        <v>12</v>
-      </c>
-      <c r="B98" s="68">
-        <v>0.19189999999999999</v>
-      </c>
-      <c r="C98" s="66">
-        <f t="shared" si="3"/>
-        <v>2.3028</v>
-      </c>
-      <c r="E98" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F98" s="77">
-        <f t="shared" si="4"/>
-        <v>0.29189999999999999</v>
-      </c>
-      <c r="H98" s="79">
-        <f t="shared" si="5"/>
-        <v>3.5027999999999997</v>
-      </c>
-      <c r="K98">
-        <v>0.29189999999999999</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="36">
-        <v>15</v>
-      </c>
-      <c r="B99" s="66">
-        <v>0.13039999999999999</v>
-      </c>
-      <c r="C99" s="66">
-        <f t="shared" si="3"/>
-        <v>1.9559999999999997</v>
-      </c>
-      <c r="E99" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F99" s="77">
-        <f t="shared" si="4"/>
-        <v>0.23039999999999999</v>
-      </c>
-      <c r="H99" s="79">
-        <f t="shared" si="5"/>
-        <v>3.456</v>
-      </c>
-      <c r="K99">
-        <v>0.23039999999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="38">
-        <v>12</v>
-      </c>
-      <c r="B100" s="68">
-        <v>0.31850000000000001</v>
-      </c>
-      <c r="C100" s="66">
-        <f t="shared" si="3"/>
-        <v>3.8220000000000001</v>
-      </c>
-      <c r="E100" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F100" s="77">
-        <f t="shared" si="4"/>
-        <v>0.41849999999999998</v>
-      </c>
-      <c r="H100" s="79">
-        <f t="shared" si="5"/>
-        <v>5.0220000000000002</v>
-      </c>
-      <c r="K100">
-        <v>0.41849999999999998</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="36">
-        <v>11</v>
-      </c>
-      <c r="B101" s="66">
-        <v>1.96</v>
-      </c>
-      <c r="C101" s="66">
-        <f t="shared" si="3"/>
-        <v>21.56</v>
-      </c>
-      <c r="E101" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F101" s="77">
-        <f t="shared" si="4"/>
-        <v>2.06</v>
-      </c>
-      <c r="H101" s="79">
-        <f t="shared" si="5"/>
-        <v>22.66</v>
-      </c>
-      <c r="K101">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="38">
-        <v>11</v>
-      </c>
-      <c r="B102" s="68">
-        <v>20.83</v>
-      </c>
-      <c r="C102" s="66">
-        <f t="shared" si="3"/>
-        <v>229.13</v>
-      </c>
-      <c r="E102" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F102" s="77">
-        <f t="shared" si="4"/>
-        <v>20.93</v>
-      </c>
-      <c r="H102" s="79">
-        <f t="shared" si="5"/>
-        <v>230.23</v>
-      </c>
-      <c r="K102">
-        <v>20.93</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="36">
-        <v>25</v>
-      </c>
-      <c r="B103" s="66">
-        <v>0.1409</v>
-      </c>
-      <c r="C103" s="66">
-        <f t="shared" si="3"/>
-        <v>3.5225</v>
-      </c>
-      <c r="E103" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F103" s="77">
-        <f t="shared" si="4"/>
-        <v>0.2409</v>
-      </c>
-      <c r="H103" s="79">
-        <f t="shared" si="5"/>
-        <v>6.0225</v>
-      </c>
-      <c r="K103">
-        <v>0.2409</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="38">
-        <v>11</v>
-      </c>
-      <c r="B104" s="68">
-        <v>0.86409999999999998</v>
-      </c>
-      <c r="C104" s="66">
-        <f t="shared" si="3"/>
-        <v>9.5051000000000005</v>
-      </c>
-      <c r="E104" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F104" s="77">
-        <f t="shared" si="4"/>
-        <v>0.96409999999999996</v>
-      </c>
-      <c r="H104" s="79">
-        <f t="shared" si="5"/>
-        <v>10.6051</v>
-      </c>
-      <c r="K104">
-        <v>0.96409999999999996</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="36">
-        <v>11</v>
-      </c>
-      <c r="B105" s="66">
-        <v>6.2104999999999997</v>
-      </c>
-      <c r="C105" s="66">
-        <f t="shared" si="3"/>
-        <v>68.3155</v>
-      </c>
-      <c r="E105" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F105" s="77">
-        <f t="shared" si="4"/>
-        <v>6.3104999999999993</v>
-      </c>
-      <c r="H105" s="79">
-        <f t="shared" si="5"/>
-        <v>69.415499999999994</v>
-      </c>
-      <c r="K105">
-        <v>6.3104999999999993</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="38">
-        <v>11</v>
-      </c>
-      <c r="B106" s="68">
-        <v>14.836</v>
-      </c>
-      <c r="C106" s="66">
-        <f t="shared" si="3"/>
-        <v>163.196</v>
-      </c>
-      <c r="E106" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F106" s="77">
-        <f t="shared" si="4"/>
-        <v>14.936</v>
-      </c>
-      <c r="H106" s="79">
-        <f t="shared" si="5"/>
-        <v>164.29599999999999</v>
-      </c>
-      <c r="K106">
-        <v>14.936</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="36">
-        <v>11</v>
-      </c>
-      <c r="B107" s="66">
-        <v>13.6875</v>
-      </c>
-      <c r="C107" s="66">
-        <f t="shared" si="3"/>
-        <v>150.5625</v>
-      </c>
-      <c r="E107" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F107" s="77">
-        <f t="shared" si="4"/>
-        <v>13.7875</v>
-      </c>
-      <c r="H107" s="79">
-        <f t="shared" si="5"/>
-        <v>151.66249999999999</v>
-      </c>
-      <c r="K107">
-        <v>13.7875</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="38">
-        <v>11</v>
-      </c>
-      <c r="B108" s="68">
-        <v>17.5</v>
-      </c>
-      <c r="C108" s="66">
-        <f t="shared" si="3"/>
-        <v>192.5</v>
-      </c>
-      <c r="E108" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F108" s="77">
-        <f t="shared" si="4"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="H108" s="79">
-        <f t="shared" si="5"/>
-        <v>193.60000000000002</v>
-      </c>
-      <c r="K108">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="36">
-        <v>22</v>
-      </c>
-      <c r="B109" s="66">
-        <v>0.34949999999999998</v>
-      </c>
-      <c r="C109" s="66">
-        <f t="shared" si="3"/>
-        <v>7.6889999999999992</v>
-      </c>
-      <c r="E109" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F109" s="77">
-        <f t="shared" si="4"/>
-        <v>0.44950000000000001</v>
-      </c>
-      <c r="H109" s="79">
-        <f t="shared" si="5"/>
-        <v>9.8889999999999993</v>
-      </c>
-      <c r="K109">
-        <v>0.44950000000000001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="38">
-        <v>15</v>
-      </c>
-      <c r="B110" s="68">
-        <v>8.6499999999999994E-2</v>
-      </c>
-      <c r="C110" s="66">
-        <f t="shared" si="3"/>
-        <v>1.2974999999999999</v>
-      </c>
-      <c r="E110" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F110" s="77">
-        <f t="shared" si="4"/>
-        <v>0.1865</v>
-      </c>
-      <c r="H110" s="79">
-        <f t="shared" si="5"/>
-        <v>2.7974999999999999</v>
-      </c>
-      <c r="K110">
-        <v>0.1865</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="36">
-        <v>11</v>
-      </c>
-      <c r="B111" s="66">
-        <v>0.1618</v>
-      </c>
-      <c r="C111" s="66">
-        <f t="shared" si="3"/>
-        <v>1.7798</v>
-      </c>
-      <c r="E111" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F111" s="77">
-        <f t="shared" si="4"/>
-        <v>0.26180000000000003</v>
-      </c>
-      <c r="H111" s="79">
-        <f t="shared" si="5"/>
-        <v>2.8798000000000004</v>
-      </c>
-      <c r="K111">
-        <v>0.26180000000000003</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="38">
-        <v>11</v>
-      </c>
-      <c r="B112" s="68">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="C112" s="66">
-        <f t="shared" si="3"/>
-        <v>2.6796000000000002</v>
-      </c>
-      <c r="E112" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="F112" s="77">
-        <f t="shared" si="4"/>
-        <v>0.34360000000000002</v>
-      </c>
-      <c r="H112" s="79">
-        <f t="shared" si="5"/>
-        <v>3.7796000000000003</v>
-      </c>
-      <c r="K112">
-        <v>0.34360000000000002</v>
-      </c>
-    </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C113" s="78">
-        <f>SUM(C3:C112)</f>
-        <v>1011.9429</v>
-      </c>
-      <c r="F113" s="77"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Deliverables/HUB/BOM/Client_BOM_Ezlo_Voice_AssistantHUB.xlsx
+++ b/Deliverables/HUB/BOM/Client_BOM_Ezlo_Voice_AssistantHUB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverables\HUB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C9F151-1C91-4840-BA60-583F120B86A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6157CD6-E7D3-4CBC-970A-A2E6EE27ED91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="515">
   <si>
     <t>Component list</t>
   </si>
@@ -2202,6 +2202,15 @@
     <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2218,15 +2227,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2600,13 +2600,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
     </row>
     <row r="2" spans="1:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2650,7 +2650,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="71"/>
+      <c r="P3" s="74"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2672,7 +2672,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="72"/>
+      <c r="P4" s="75"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2694,7 +2694,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="72"/>
+      <c r="P5" s="75"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2712,7 +2712,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="72"/>
+      <c r="P6" s="75"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2730,7 +2730,7 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="72"/>
+      <c r="P7" s="75"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2748,7 +2748,7 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="72"/>
+      <c r="P8" s="75"/>
     </row>
     <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -7174,26 +7174,28 @@
       <c r="D101" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="E101" s="75" t="s">
+      <c r="E101" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="F101" s="76" t="s">
+      <c r="F101" s="71" t="s">
         <v>487</v>
       </c>
-      <c r="G101" s="75" t="s">
+      <c r="G101" s="70" t="s">
         <v>266</v>
       </c>
-      <c r="H101" s="76"/>
-      <c r="I101" s="76" t="s">
+      <c r="H101" s="71" t="s">
+        <v>480</v>
+      </c>
+      <c r="I101" s="71" t="s">
         <v>393</v>
       </c>
-      <c r="J101" s="76" t="s">
-        <v>480</v>
-      </c>
-      <c r="K101" s="75">
+      <c r="J101" s="71" t="s">
+        <v>480</v>
+      </c>
+      <c r="K101" s="70">
         <v>1</v>
       </c>
-      <c r="L101" s="76">
+      <c r="L101" s="71">
         <v>11</v>
       </c>
       <c r="M101" s="64" t="s">
@@ -7202,7 +7204,7 @@
       <c r="N101" s="65">
         <v>0.3</v>
       </c>
-      <c r="O101" s="77">
+      <c r="O101" s="72">
         <f t="shared" si="2"/>
         <v>3.3</v>
       </c>
@@ -8084,11 +8086,11 @@
       <c r="I120" s="34"/>
       <c r="J120" s="35"/>
       <c r="K120" s="35"/>
-      <c r="L120" s="73" t="s">
+      <c r="L120" s="76" t="s">
         <v>510</v>
       </c>
-      <c r="M120" s="74"/>
-      <c r="N120" s="74"/>
+      <c r="M120" s="77"/>
+      <c r="N120" s="77"/>
       <c r="O120" s="66">
         <f>SUM(O10:O119)</f>
         <v>1787.6428999999998</v>
@@ -8107,11 +8109,11 @@
       <c r="I121" s="9"/>
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
-      <c r="L121" s="73" t="s">
+      <c r="L121" s="76" t="s">
         <v>511</v>
       </c>
-      <c r="M121" s="74"/>
-      <c r="N121" s="74"/>
+      <c r="M121" s="77"/>
+      <c r="N121" s="77"/>
       <c r="O121" s="67">
         <f>O120/10</f>
         <v>178.76428999999999</v>

--- a/Deliverables/HUB/BOM/Client_BOM_Ezlo_Voice_AssistantHUB.xlsx
+++ b/Deliverables/HUB/BOM/Client_BOM_Ezlo_Voice_AssistantHUB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverables\HUB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6157CD6-E7D3-4CBC-970A-A2E6EE27ED91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F702FE6E-EABA-41AB-8B1E-62B414FBE125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="514">
   <si>
     <t>Component list</t>
   </si>
@@ -1550,9 +1550,6 @@
     <t>0603WAJ0220T5E</t>
   </si>
   <si>
-    <t>Links</t>
-  </si>
-  <si>
     <t>Unit Cost (10 Boards)</t>
   </si>
   <si>
@@ -1574,7 +1571,7 @@
     <t>[HUB_Design]</t>
   </si>
   <si>
-    <t>Self Supplier</t>
+    <t>Quantity (10 Boards)</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1583,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1720,14 +1717,6 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2008,11 +1997,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2178,13 +2166,7 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2196,19 +2178,19 @@
     <xf numFmtId="166" fontId="14" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2220,17 +2202,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2583,8 +2564,8 @@
     <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="29.42578125" customWidth="1"/>
@@ -2600,13 +2581,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
     </row>
     <row r="2" spans="1:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2617,7 +2598,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="52" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -2639,7 +2620,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="53" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
@@ -2650,7 +2631,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="74"/>
+      <c r="P3" s="72"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2661,18 +2642,18 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="54" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="75"/>
+      <c r="P4" s="73"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2694,7 +2675,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="75"/>
+      <c r="P5" s="73"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2712,7 +2693,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="75"/>
+      <c r="P6" s="73"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2730,7 +2711,7 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="75"/>
+      <c r="P7" s="73"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2748,7 +2729,7 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="75"/>
+      <c r="P8" s="73"/>
     </row>
     <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2783,16 +2764,16 @@
         <v>461</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M9" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="N9" s="29" t="s">
         <v>506</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="O9" s="29" t="s">
         <v>507</v>
-      </c>
-      <c r="O9" s="29" t="s">
-        <v>508</v>
       </c>
       <c r="P9" s="56" t="s">
         <v>465</v>
@@ -2832,16 +2813,17 @@
         <v>1</v>
       </c>
       <c r="L10" s="36">
+        <f>K10*10</f>
+        <v>10</v>
+      </c>
+      <c r="M10" s="36">
         <v>12</v>
       </c>
-      <c r="M10" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N10" s="69">
+      <c r="N10" s="67">
         <v>0.21779999999999999</v>
       </c>
-      <c r="O10" s="63">
-        <f>N10*L10</f>
+      <c r="O10" s="62">
+        <f t="shared" ref="O10:O41" si="0">N10*M10</f>
         <v>2.6135999999999999</v>
       </c>
       <c r="P10" s="36"/>
@@ -2849,7 +2831,7 @@
     <row r="11" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="50">
-        <f t="shared" ref="B11:B119" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B119" si="1">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="58" t="s">
@@ -2880,16 +2862,17 @@
         <v>1</v>
       </c>
       <c r="L11" s="38">
+        <f t="shared" ref="L11:L74" si="2">K11*10</f>
+        <v>10</v>
+      </c>
+      <c r="M11" s="38">
         <v>15</v>
       </c>
-      <c r="M11" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N11" s="65">
+      <c r="N11" s="63">
         <v>0.20350000000000001</v>
       </c>
-      <c r="O11" s="65">
-        <f t="shared" ref="O11:O74" si="1">N11*L11</f>
+      <c r="O11" s="63">
+        <f t="shared" si="0"/>
         <v>3.0525000000000002</v>
       </c>
       <c r="P11" s="38"/>
@@ -2928,16 +2911,17 @@
         <v>3</v>
       </c>
       <c r="L12" s="36">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M12" s="36">
         <v>100</v>
       </c>
-      <c r="M12" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N12" s="63">
+      <c r="N12" s="62">
         <v>0.10210000000000001</v>
       </c>
-      <c r="O12" s="63">
-        <f t="shared" si="1"/>
+      <c r="O12" s="62">
+        <f t="shared" si="0"/>
         <v>10.210000000000001</v>
       </c>
       <c r="P12" s="36"/>
@@ -2945,7 +2929,7 @@
     <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="C13" s="58" t="s">
@@ -2976,16 +2960,17 @@
         <v>5</v>
       </c>
       <c r="L13" s="38">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="M13" s="38">
         <v>100</v>
       </c>
-      <c r="M13" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N13" s="65">
+      <c r="N13" s="63">
         <v>0.10300000000000001</v>
       </c>
-      <c r="O13" s="65">
-        <f t="shared" si="1"/>
+      <c r="O13" s="63">
+        <f t="shared" si="0"/>
         <v>10.3</v>
       </c>
       <c r="P13" s="38"/>
@@ -3024,16 +3009,17 @@
         <v>7</v>
       </c>
       <c r="L14" s="36">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="M14" s="36">
         <v>80</v>
       </c>
-      <c r="M14" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N14" s="63">
+      <c r="N14" s="62">
         <v>0.11810000000000001</v>
       </c>
-      <c r="O14" s="63">
-        <f t="shared" si="1"/>
+      <c r="O14" s="62">
+        <f t="shared" si="0"/>
         <v>9.4480000000000004</v>
       </c>
       <c r="P14" s="36"/>
@@ -3041,7 +3027,7 @@
     <row r="15" spans="1:16" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="C15" s="58" t="s">
@@ -3072,16 +3058,17 @@
         <v>126</v>
       </c>
       <c r="L15" s="38">
+        <f t="shared" si="2"/>
+        <v>1260</v>
+      </c>
+      <c r="M15" s="38">
         <v>1300</v>
       </c>
-      <c r="M15" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N15" s="65">
+      <c r="N15" s="63">
         <v>0.1009</v>
       </c>
-      <c r="O15" s="65">
-        <f t="shared" si="1"/>
+      <c r="O15" s="63">
+        <f t="shared" si="0"/>
         <v>131.17000000000002</v>
       </c>
       <c r="P15" s="38"/>
@@ -3120,16 +3107,17 @@
         <v>16</v>
       </c>
       <c r="L16" s="36">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="M16" s="36">
         <v>180</v>
       </c>
-      <c r="M16" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N16" s="63">
+      <c r="N16" s="62">
         <v>0.11420000000000001</v>
       </c>
-      <c r="O16" s="63">
-        <f t="shared" si="1"/>
+      <c r="O16" s="62">
+        <f t="shared" si="0"/>
         <v>20.556000000000001</v>
       </c>
       <c r="P16" s="36"/>
@@ -3137,7 +3125,7 @@
     <row r="17" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -3168,16 +3156,17 @@
         <v>25</v>
       </c>
       <c r="L17" s="38">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="M17" s="38">
         <v>280</v>
       </c>
-      <c r="M17" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N17" s="65">
+      <c r="N17" s="63">
         <v>0.11360000000000001</v>
       </c>
-      <c r="O17" s="65">
-        <f t="shared" si="1"/>
+      <c r="O17" s="63">
+        <f t="shared" si="0"/>
         <v>31.808000000000003</v>
       </c>
       <c r="P17" s="38"/>
@@ -3216,16 +3205,17 @@
         <v>27</v>
       </c>
       <c r="L18" s="36">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+      <c r="M18" s="36">
         <v>300</v>
       </c>
-      <c r="M18" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N18" s="63">
+      <c r="N18" s="62">
         <v>0.1052</v>
       </c>
-      <c r="O18" s="63">
-        <f t="shared" si="1"/>
+      <c r="O18" s="62">
+        <f t="shared" si="0"/>
         <v>31.560000000000002</v>
       </c>
       <c r="P18" s="36"/>
@@ -3233,7 +3223,7 @@
     <row r="19" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C19" s="58" t="s">
@@ -3264,16 +3254,17 @@
         <v>9</v>
       </c>
       <c r="L19" s="38">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="M19" s="38">
         <v>100</v>
       </c>
-      <c r="M19" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N19" s="65">
+      <c r="N19" s="63">
         <v>0.10310000000000001</v>
       </c>
-      <c r="O19" s="65">
-        <f t="shared" si="1"/>
+      <c r="O19" s="63">
+        <f t="shared" si="0"/>
         <v>10.31</v>
       </c>
       <c r="P19" s="38"/>
@@ -3312,16 +3303,17 @@
         <v>4</v>
       </c>
       <c r="L20" s="36">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="M20" s="36">
         <v>50</v>
       </c>
-      <c r="M20" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N20" s="63">
+      <c r="N20" s="62">
         <v>0.10750000000000001</v>
       </c>
-      <c r="O20" s="63">
-        <f t="shared" si="1"/>
+      <c r="O20" s="62">
+        <f t="shared" si="0"/>
         <v>5.3750000000000009</v>
       </c>
       <c r="P20" s="36"/>
@@ -3329,7 +3321,7 @@
     <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="C21" s="58" t="s">
@@ -3360,16 +3352,17 @@
         <v>6</v>
       </c>
       <c r="L21" s="38">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="M21" s="38">
         <v>100</v>
       </c>
-      <c r="M21" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N21" s="65">
+      <c r="N21" s="63">
         <v>0.10290000000000001</v>
       </c>
-      <c r="O21" s="65">
-        <f t="shared" si="1"/>
+      <c r="O21" s="63">
+        <f t="shared" si="0"/>
         <v>10.290000000000001</v>
       </c>
       <c r="P21" s="38"/>
@@ -3408,16 +3401,17 @@
         <v>1</v>
       </c>
       <c r="L22" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M22" s="36">
         <v>50</v>
       </c>
-      <c r="M22" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N22" s="63">
+      <c r="N22" s="62">
         <v>0.11330000000000001</v>
       </c>
-      <c r="O22" s="63">
-        <f t="shared" si="1"/>
+      <c r="O22" s="62">
+        <f t="shared" si="0"/>
         <v>5.6650000000000009</v>
       </c>
       <c r="P22" s="36"/>
@@ -3425,7 +3419,7 @@
     <row r="23" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="C23" s="58" t="s">
@@ -3456,16 +3450,17 @@
         <v>2</v>
       </c>
       <c r="L23" s="38">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M23" s="38">
         <v>100</v>
       </c>
-      <c r="M23" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N23" s="65">
+      <c r="N23" s="63">
         <v>0.1027</v>
       </c>
-      <c r="O23" s="65">
-        <f t="shared" si="1"/>
+      <c r="O23" s="63">
+        <f t="shared" si="0"/>
         <v>10.27</v>
       </c>
       <c r="P23" s="38"/>
@@ -3504,16 +3499,17 @@
         <v>2</v>
       </c>
       <c r="L24" s="36">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M24" s="36">
         <v>50</v>
       </c>
-      <c r="M24" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N24" s="63">
+      <c r="N24" s="62">
         <v>0.115</v>
       </c>
-      <c r="O24" s="63">
-        <f t="shared" si="1"/>
+      <c r="O24" s="62">
+        <f t="shared" si="0"/>
         <v>5.75</v>
       </c>
       <c r="P24" s="36"/>
@@ -3521,7 +3517,7 @@
     <row r="25" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="C25" s="58" t="s">
@@ -3552,16 +3548,17 @@
         <v>10</v>
       </c>
       <c r="L25" s="38">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="M25" s="38">
         <v>150</v>
       </c>
-      <c r="M25" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N25" s="65">
+      <c r="N25" s="63">
         <v>0.10700000000000001</v>
       </c>
-      <c r="O25" s="65">
-        <f t="shared" si="1"/>
+      <c r="O25" s="63">
+        <f t="shared" si="0"/>
         <v>16.05</v>
       </c>
       <c r="P25" s="38"/>
@@ -3600,16 +3597,17 @@
         <v>4</v>
       </c>
       <c r="L26" s="36">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="M26" s="36">
         <v>100</v>
       </c>
-      <c r="M26" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N26" s="63">
+      <c r="N26" s="62">
         <v>0.1028</v>
       </c>
-      <c r="O26" s="63">
-        <f t="shared" si="1"/>
+      <c r="O26" s="62">
+        <f t="shared" si="0"/>
         <v>10.280000000000001</v>
       </c>
       <c r="P26" s="36"/>
@@ -3617,7 +3615,7 @@
     <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C27" s="58" t="s">
@@ -3648,16 +3646,17 @@
         <v>8</v>
       </c>
       <c r="L27" s="38">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="M27" s="38">
         <v>100</v>
       </c>
-      <c r="M27" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N27" s="65">
+      <c r="N27" s="63">
         <v>0.1202</v>
       </c>
-      <c r="O27" s="65">
-        <f t="shared" si="1"/>
+      <c r="O27" s="63">
+        <f t="shared" si="0"/>
         <v>12.02</v>
       </c>
       <c r="P27" s="38"/>
@@ -3696,16 +3695,17 @@
         <v>6</v>
       </c>
       <c r="L28" s="36">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="M28" s="36">
         <v>100</v>
       </c>
-      <c r="M28" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N28" s="63">
+      <c r="N28" s="62">
         <v>0.11950000000000001</v>
       </c>
-      <c r="O28" s="63">
-        <f t="shared" si="1"/>
+      <c r="O28" s="62">
+        <f t="shared" si="0"/>
         <v>11.950000000000001</v>
       </c>
       <c r="P28" s="36"/>
@@ -3713,7 +3713,7 @@
     <row r="29" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C29" s="58" t="s">
@@ -3744,16 +3744,17 @@
         <v>3</v>
       </c>
       <c r="L29" s="38">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M29" s="38">
         <v>40</v>
       </c>
-      <c r="M29" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N29" s="65">
+      <c r="N29" s="63">
         <v>0.1477</v>
       </c>
-      <c r="O29" s="65">
-        <f t="shared" si="1"/>
+      <c r="O29" s="63">
+        <f t="shared" si="0"/>
         <v>5.9079999999999995</v>
       </c>
       <c r="P29" s="38"/>
@@ -3792,16 +3793,17 @@
         <v>8</v>
       </c>
       <c r="L30" s="36">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="M30" s="36">
         <v>100</v>
       </c>
-      <c r="M30" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N30" s="63">
+      <c r="N30" s="62">
         <v>0.12920000000000001</v>
       </c>
-      <c r="O30" s="63">
-        <f t="shared" si="1"/>
+      <c r="O30" s="62">
+        <f t="shared" si="0"/>
         <v>12.920000000000002</v>
       </c>
       <c r="P30" s="36"/>
@@ -3809,7 +3811,7 @@
     <row r="31" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C31" s="58" t="s">
@@ -3840,16 +3842,17 @@
         <v>5</v>
       </c>
       <c r="L31" s="38">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="M31" s="38">
         <v>55</v>
       </c>
-      <c r="M31" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N31" s="65">
+      <c r="N31" s="63">
         <v>0.21610000000000001</v>
       </c>
-      <c r="O31" s="65">
-        <f t="shared" si="1"/>
+      <c r="O31" s="63">
+        <f t="shared" si="0"/>
         <v>11.8855</v>
       </c>
       <c r="P31" s="38"/>
@@ -3888,16 +3891,17 @@
         <v>3</v>
       </c>
       <c r="L32" s="36">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M32" s="36">
         <v>35</v>
       </c>
-      <c r="M32" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N32" s="63">
+      <c r="N32" s="62">
         <v>0.18359999999999999</v>
       </c>
-      <c r="O32" s="63">
-        <f t="shared" si="1"/>
+      <c r="O32" s="62">
+        <f t="shared" si="0"/>
         <v>6.4259999999999993</v>
       </c>
       <c r="P32" s="36"/>
@@ -3905,7 +3909,7 @@
     <row r="33" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="C33" s="58" t="s">
@@ -3936,16 +3940,17 @@
         <v>1</v>
       </c>
       <c r="L33" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M33" s="38">
         <v>12</v>
       </c>
-      <c r="M33" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N33" s="65">
+      <c r="N33" s="63">
         <v>0.41849999999999998</v>
       </c>
-      <c r="O33" s="65">
-        <f t="shared" si="1"/>
+      <c r="O33" s="63">
+        <f t="shared" si="0"/>
         <v>5.0220000000000002</v>
       </c>
       <c r="P33" s="38"/>
@@ -3984,16 +3989,17 @@
         <v>1</v>
       </c>
       <c r="L34" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M34" s="36">
         <v>20</v>
       </c>
-      <c r="M34" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N34" s="63">
+      <c r="N34" s="62">
         <v>0.13620000000000002</v>
       </c>
-      <c r="O34" s="63">
-        <f t="shared" si="1"/>
+      <c r="O34" s="62">
+        <f t="shared" si="0"/>
         <v>2.7240000000000002</v>
       </c>
       <c r="P34" s="36"/>
@@ -4001,7 +4007,7 @@
     <row r="35" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="C35" s="58" t="s">
@@ -4032,16 +4038,17 @@
         <v>1</v>
       </c>
       <c r="L35" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M35" s="38">
         <v>20</v>
       </c>
-      <c r="M35" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N35" s="65">
+      <c r="N35" s="63">
         <v>0.14900000000000002</v>
       </c>
-      <c r="O35" s="65">
-        <f t="shared" si="1"/>
+      <c r="O35" s="63">
+        <f t="shared" si="0"/>
         <v>2.9800000000000004</v>
       </c>
       <c r="P35" s="38"/>
@@ -4080,16 +4087,17 @@
         <v>1</v>
       </c>
       <c r="L36" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M36" s="36">
         <v>20</v>
       </c>
-      <c r="M36" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N36" s="63">
+      <c r="N36" s="62">
         <v>0.12820000000000001</v>
       </c>
-      <c r="O36" s="63">
-        <f t="shared" si="1"/>
+      <c r="O36" s="62">
+        <f t="shared" si="0"/>
         <v>2.5640000000000001</v>
       </c>
       <c r="P36" s="36"/>
@@ -4097,7 +4105,7 @@
     <row r="37" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="C37" s="58" t="s">
@@ -4128,16 +4136,17 @@
         <v>1</v>
       </c>
       <c r="L37" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M37" s="38">
         <v>12</v>
       </c>
-      <c r="M37" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N37" s="65">
+      <c r="N37" s="63">
         <v>0.67669999999999997</v>
       </c>
-      <c r="O37" s="65">
-        <f t="shared" si="1"/>
+      <c r="O37" s="63">
+        <f t="shared" si="0"/>
         <v>8.1204000000000001</v>
       </c>
       <c r="P37" s="38"/>
@@ -4176,16 +4185,17 @@
         <v>1</v>
       </c>
       <c r="L38" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M38" s="36">
         <v>11</v>
       </c>
-      <c r="M38" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N38" s="63">
+      <c r="N38" s="62">
         <v>0.23469999999999999</v>
       </c>
-      <c r="O38" s="63">
-        <f t="shared" si="1"/>
+      <c r="O38" s="62">
+        <f t="shared" si="0"/>
         <v>2.5817000000000001</v>
       </c>
       <c r="P38" s="36"/>
@@ -4193,7 +4203,7 @@
     <row r="39" spans="1:16" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C39" s="58" t="s">
@@ -4224,16 +4234,17 @@
         <v>1</v>
       </c>
       <c r="L39" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M39" s="38">
         <v>12</v>
       </c>
-      <c r="M39" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N39" s="65">
+      <c r="N39" s="63">
         <v>0.23569999999999999</v>
       </c>
-      <c r="O39" s="65">
-        <f t="shared" si="1"/>
+      <c r="O39" s="63">
+        <f t="shared" si="0"/>
         <v>2.8283999999999998</v>
       </c>
       <c r="P39" s="38"/>
@@ -4272,16 +4283,17 @@
         <v>1</v>
       </c>
       <c r="L40" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M40" s="36">
         <v>11</v>
       </c>
-      <c r="M40" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N40" s="63">
+      <c r="N40" s="62">
         <v>1.8351000000000002</v>
       </c>
-      <c r="O40" s="63">
-        <f t="shared" si="1"/>
+      <c r="O40" s="62">
+        <f t="shared" si="0"/>
         <v>20.186100000000003</v>
       </c>
       <c r="P40" s="36"/>
@@ -4289,7 +4301,7 @@
     <row r="41" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="C41" s="58" t="s">
@@ -4320,16 +4332,17 @@
         <v>1</v>
       </c>
       <c r="L41" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M41" s="38">
         <v>12</v>
       </c>
-      <c r="M41" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N41" s="65">
+      <c r="N41" s="63">
         <v>0.52870000000000006</v>
       </c>
-      <c r="O41" s="65">
-        <f t="shared" si="1"/>
+      <c r="O41" s="63">
+        <f t="shared" si="0"/>
         <v>6.3444000000000003</v>
       </c>
       <c r="P41" s="38"/>
@@ -4368,16 +4381,17 @@
         <v>2</v>
       </c>
       <c r="L42" s="36">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M42" s="36">
         <v>25</v>
       </c>
-      <c r="M42" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N42" s="63">
+      <c r="N42" s="62">
         <v>0.1875</v>
       </c>
-      <c r="O42" s="63">
-        <f t="shared" si="1"/>
+      <c r="O42" s="62">
+        <f t="shared" ref="O42:O73" si="3">N42*M42</f>
         <v>4.6875</v>
       </c>
       <c r="P42" s="36"/>
@@ -4385,7 +4399,7 @@
     <row r="43" spans="1:16" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="C43" s="58" t="s">
@@ -4416,16 +4430,17 @@
         <v>1</v>
       </c>
       <c r="L43" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M43" s="38">
         <v>20</v>
       </c>
-      <c r="M43" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N43" s="65">
+      <c r="N43" s="63">
         <v>0.1447</v>
       </c>
-      <c r="O43" s="65">
-        <f t="shared" si="1"/>
+      <c r="O43" s="63">
+        <f t="shared" si="3"/>
         <v>2.8940000000000001</v>
       </c>
       <c r="P43" s="38"/>
@@ -4464,16 +4479,17 @@
         <v>1</v>
       </c>
       <c r="L44" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M44" s="36">
         <v>12</v>
       </c>
-      <c r="M44" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N44" s="63">
+      <c r="N44" s="62">
         <v>0.40129999999999999</v>
       </c>
-      <c r="O44" s="63">
-        <f t="shared" si="1"/>
+      <c r="O44" s="62">
+        <f t="shared" si="3"/>
         <v>4.8155999999999999</v>
       </c>
       <c r="P44" s="36"/>
@@ -4481,7 +4497,7 @@
     <row r="45" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C45" s="58" t="s">
@@ -4512,16 +4528,17 @@
         <v>1</v>
       </c>
       <c r="L45" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M45" s="38">
         <v>12</v>
       </c>
-      <c r="M45" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N45" s="65">
+      <c r="N45" s="63">
         <v>0.76449999999999996</v>
       </c>
-      <c r="O45" s="65">
-        <f t="shared" si="1"/>
+      <c r="O45" s="63">
+        <f t="shared" si="3"/>
         <v>9.1739999999999995</v>
       </c>
       <c r="P45" s="38"/>
@@ -4560,16 +4577,17 @@
         <v>1</v>
       </c>
       <c r="L46" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M46" s="36">
         <v>12</v>
       </c>
-      <c r="M46" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N46" s="63">
+      <c r="N46" s="62">
         <v>0.27039999999999997</v>
       </c>
-      <c r="O46" s="63">
-        <f t="shared" si="1"/>
+      <c r="O46" s="62">
+        <f t="shared" si="3"/>
         <v>3.2447999999999997</v>
       </c>
       <c r="P46" s="36"/>
@@ -4577,7 +4595,7 @@
     <row r="47" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="C47" s="58" t="s">
@@ -4608,16 +4626,17 @@
         <v>1</v>
       </c>
       <c r="L47" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M47" s="38">
         <v>20</v>
       </c>
-      <c r="M47" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N47" s="65">
+      <c r="N47" s="63">
         <v>0.1515</v>
       </c>
-      <c r="O47" s="65">
-        <f t="shared" si="1"/>
+      <c r="O47" s="63">
+        <f t="shared" si="3"/>
         <v>3.03</v>
       </c>
       <c r="P47" s="38"/>
@@ -4656,16 +4675,17 @@
         <v>2</v>
       </c>
       <c r="L48" s="36">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M48" s="36">
         <v>30</v>
       </c>
-      <c r="M48" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N48" s="63">
+      <c r="N48" s="62">
         <v>0.16090000000000002</v>
       </c>
-      <c r="O48" s="63">
-        <f t="shared" si="1"/>
+      <c r="O48" s="62">
+        <f t="shared" si="3"/>
         <v>4.8270000000000008</v>
       </c>
       <c r="P48" s="36"/>
@@ -4673,7 +4693,7 @@
     <row r="49" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="C49" s="58" t="s">
@@ -4704,16 +4724,17 @@
         <v>1</v>
       </c>
       <c r="L49" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M49" s="38">
         <v>12</v>
       </c>
-      <c r="M49" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N49" s="65">
+      <c r="N49" s="63">
         <v>0.24030000000000001</v>
       </c>
-      <c r="O49" s="65">
-        <f t="shared" si="1"/>
+      <c r="O49" s="63">
+        <f t="shared" si="3"/>
         <v>2.8836000000000004</v>
       </c>
       <c r="P49" s="38"/>
@@ -4752,16 +4773,17 @@
         <v>2</v>
       </c>
       <c r="L50" s="36">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M50" s="36">
         <v>30</v>
       </c>
-      <c r="M50" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N50" s="63">
+      <c r="N50" s="62">
         <v>0.14380000000000001</v>
       </c>
-      <c r="O50" s="63">
-        <f t="shared" si="1"/>
+      <c r="O50" s="62">
+        <f t="shared" si="3"/>
         <v>4.3140000000000001</v>
       </c>
       <c r="P50" s="36"/>
@@ -4769,7 +4791,7 @@
     <row r="51" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="C51" s="58" t="s">
@@ -4800,16 +4822,17 @@
         <v>2</v>
       </c>
       <c r="L51" s="38">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M51" s="38">
         <v>22</v>
       </c>
-      <c r="M51" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N51" s="65">
+      <c r="N51" s="63">
         <v>0.23650000000000002</v>
       </c>
-      <c r="O51" s="65">
-        <f t="shared" si="1"/>
+      <c r="O51" s="63">
+        <f t="shared" si="3"/>
         <v>5.2030000000000003</v>
       </c>
       <c r="P51" s="38"/>
@@ -4848,16 +4871,17 @@
         <v>2</v>
       </c>
       <c r="L52" s="36">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M52" s="36">
         <v>22</v>
       </c>
-      <c r="M52" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N52" s="63">
+      <c r="N52" s="62">
         <v>0.248</v>
       </c>
-      <c r="O52" s="63">
-        <f t="shared" si="1"/>
+      <c r="O52" s="62">
+        <f t="shared" si="3"/>
         <v>5.4559999999999995</v>
       </c>
       <c r="P52" s="36"/>
@@ -4865,7 +4889,7 @@
     <row r="53" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="C53" s="58" t="s">
@@ -4896,16 +4920,17 @@
         <v>1</v>
       </c>
       <c r="L53" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M53" s="38">
         <v>20</v>
       </c>
-      <c r="M53" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N53" s="65">
+      <c r="N53" s="63">
         <v>0.1706</v>
       </c>
-      <c r="O53" s="65">
-        <f t="shared" si="1"/>
+      <c r="O53" s="63">
+        <f t="shared" si="3"/>
         <v>3.4119999999999999</v>
       </c>
       <c r="P53" s="38"/>
@@ -4944,16 +4969,17 @@
         <v>1</v>
       </c>
       <c r="L54" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M54" s="36">
         <v>100</v>
       </c>
-      <c r="M54" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N54" s="63">
+      <c r="N54" s="62">
         <v>0.10310000000000001</v>
       </c>
-      <c r="O54" s="63">
-        <f t="shared" si="1"/>
+      <c r="O54" s="62">
+        <f t="shared" si="3"/>
         <v>10.31</v>
       </c>
       <c r="P54" s="36"/>
@@ -4961,7 +4987,7 @@
     <row r="55" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="C55" s="58" t="s">
@@ -4992,16 +5018,17 @@
         <v>1</v>
       </c>
       <c r="L55" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M55" s="38">
         <v>20</v>
       </c>
-      <c r="M55" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N55" s="65">
+      <c r="N55" s="63">
         <v>0.15620000000000001</v>
       </c>
-      <c r="O55" s="65">
-        <f t="shared" si="1"/>
+      <c r="O55" s="63">
+        <f t="shared" si="3"/>
         <v>3.1240000000000001</v>
       </c>
       <c r="P55" s="38"/>
@@ -5040,16 +5067,17 @@
         <v>1</v>
       </c>
       <c r="L56" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M56" s="36">
         <v>50</v>
       </c>
-      <c r="M56" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N56" s="63">
+      <c r="N56" s="62">
         <v>0.1163</v>
       </c>
-      <c r="O56" s="63">
-        <f t="shared" si="1"/>
+      <c r="O56" s="62">
+        <f t="shared" si="3"/>
         <v>5.8150000000000004</v>
       </c>
       <c r="P56" s="36"/>
@@ -5057,7 +5085,7 @@
     <row r="57" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C57" s="58" t="s">
@@ -5088,16 +5116,17 @@
         <v>1</v>
       </c>
       <c r="L57" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M57" s="38">
         <v>20</v>
       </c>
-      <c r="M57" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N57" s="65">
+      <c r="N57" s="63">
         <v>0.13540000000000002</v>
       </c>
-      <c r="O57" s="65">
-        <f t="shared" si="1"/>
+      <c r="O57" s="63">
+        <f t="shared" si="3"/>
         <v>2.7080000000000002</v>
       </c>
       <c r="P57" s="38"/>
@@ -5136,16 +5165,17 @@
         <v>1</v>
       </c>
       <c r="L58" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M58" s="36">
         <v>20</v>
       </c>
-      <c r="M58" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N58" s="63">
+      <c r="N58" s="62">
         <v>0.13520000000000001</v>
       </c>
-      <c r="O58" s="63">
-        <f t="shared" si="1"/>
+      <c r="O58" s="62">
+        <f t="shared" si="3"/>
         <v>2.7040000000000002</v>
       </c>
       <c r="P58" s="36"/>
@@ -5153,7 +5183,7 @@
     <row r="59" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="C59" s="58" t="s">
@@ -5184,14 +5214,17 @@
         <v>1</v>
       </c>
       <c r="L59" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M59" s="38">
         <v>50</v>
       </c>
-      <c r="M59" s="64"/>
-      <c r="N59" s="65">
+      <c r="N59" s="63">
         <v>0.1159</v>
       </c>
-      <c r="O59" s="65">
-        <f t="shared" si="1"/>
+      <c r="O59" s="63">
+        <f t="shared" si="3"/>
         <v>5.7949999999999999</v>
       </c>
       <c r="P59" s="38"/>
@@ -5229,16 +5262,17 @@
       <c r="K60" s="37">
         <v>28</v>
       </c>
-      <c r="L60" s="36" t="s">
-        <v>480</v>
-      </c>
-      <c r="M60" s="62" t="s">
-        <v>480</v>
-      </c>
-      <c r="N60" s="63">
+      <c r="L60" s="36">
+        <f t="shared" si="2"/>
+        <v>280</v>
+      </c>
+      <c r="M60" s="36" t="s">
+        <v>480</v>
+      </c>
+      <c r="N60" s="62">
         <v>0</v>
       </c>
-      <c r="O60" s="63" t="s">
+      <c r="O60" s="62" t="s">
         <v>480</v>
       </c>
       <c r="P60" s="36"/>
@@ -5246,7 +5280,7 @@
     <row r="61" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="C61" s="58" t="s">
@@ -5277,16 +5311,17 @@
         <v>10</v>
       </c>
       <c r="L61" s="38">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="M61" s="38">
         <v>150</v>
       </c>
-      <c r="M61" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N61" s="65">
+      <c r="N61" s="63">
         <v>0.11360000000000001</v>
       </c>
-      <c r="O61" s="65">
-        <f t="shared" si="1"/>
+      <c r="O61" s="63">
+        <f t="shared" ref="O61:O98" si="4">N61*M61</f>
         <v>17.040000000000003</v>
       </c>
       <c r="P61" s="38"/>
@@ -5325,16 +5360,17 @@
         <v>1</v>
       </c>
       <c r="L62" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M62" s="36">
         <v>20</v>
       </c>
-      <c r="M62" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N62" s="63">
+      <c r="N62" s="62">
         <v>0.13150000000000001</v>
       </c>
-      <c r="O62" s="63">
-        <f t="shared" si="1"/>
+      <c r="O62" s="62">
+        <f t="shared" si="4"/>
         <v>2.63</v>
       </c>
       <c r="P62" s="36"/>
@@ -5342,7 +5378,7 @@
     <row r="63" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C63" s="58" t="s">
@@ -5373,16 +5409,17 @@
         <v>1</v>
       </c>
       <c r="L63" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M63" s="38">
         <v>50</v>
       </c>
-      <c r="M63" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N63" s="65">
+      <c r="N63" s="63">
         <v>0.11650000000000001</v>
       </c>
-      <c r="O63" s="65">
-        <f t="shared" si="1"/>
+      <c r="O63" s="63">
+        <f t="shared" si="4"/>
         <v>5.8250000000000002</v>
       </c>
       <c r="P63" s="38"/>
@@ -5421,16 +5458,17 @@
         <v>1</v>
       </c>
       <c r="L64" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M64" s="36">
         <v>20</v>
       </c>
-      <c r="M64" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N64" s="63">
+      <c r="N64" s="62">
         <v>0.13670000000000002</v>
       </c>
-      <c r="O64" s="63">
-        <f t="shared" si="1"/>
+      <c r="O64" s="62">
+        <f t="shared" si="4"/>
         <v>2.7340000000000004</v>
       </c>
       <c r="P64" s="36"/>
@@ -5438,7 +5476,7 @@
     <row r="65" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="C65" s="58" t="s">
@@ -5469,16 +5507,17 @@
         <v>5</v>
       </c>
       <c r="L65" s="38">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="M65" s="38">
         <v>60</v>
       </c>
-      <c r="M65" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N65" s="65">
+      <c r="N65" s="63">
         <v>0.12050000000000001</v>
       </c>
-      <c r="O65" s="65">
-        <f t="shared" si="1"/>
+      <c r="O65" s="63">
+        <f t="shared" si="4"/>
         <v>7.23</v>
       </c>
       <c r="P65" s="38"/>
@@ -5517,16 +5556,17 @@
         <v>3</v>
       </c>
       <c r="L66" s="36">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M66" s="36">
         <v>40</v>
       </c>
-      <c r="M66" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N66" s="63">
+      <c r="N66" s="62">
         <v>0.13140000000000002</v>
       </c>
-      <c r="O66" s="63">
-        <f t="shared" si="1"/>
+      <c r="O66" s="62">
+        <f t="shared" si="4"/>
         <v>5.2560000000000002</v>
       </c>
       <c r="P66" s="36"/>
@@ -5534,7 +5574,7 @@
     <row r="67" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="C67" s="58" t="s">
@@ -5565,16 +5605,17 @@
         <v>1</v>
       </c>
       <c r="L67" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M67" s="38">
         <v>20</v>
       </c>
-      <c r="M67" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N67" s="65">
+      <c r="N67" s="63">
         <v>0.14960000000000001</v>
       </c>
-      <c r="O67" s="65">
-        <f t="shared" si="1"/>
+      <c r="O67" s="63">
+        <f t="shared" si="4"/>
         <v>2.992</v>
       </c>
       <c r="P67" s="38"/>
@@ -5613,16 +5654,17 @@
         <v>37</v>
       </c>
       <c r="L68" s="36">
+        <f t="shared" si="2"/>
+        <v>370</v>
+      </c>
+      <c r="M68" s="36">
         <v>400</v>
       </c>
-      <c r="M68" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N68" s="63">
+      <c r="N68" s="62">
         <v>0.1017</v>
       </c>
-      <c r="O68" s="63">
-        <f t="shared" si="1"/>
+      <c r="O68" s="62">
+        <f t="shared" si="4"/>
         <v>40.68</v>
       </c>
       <c r="P68" s="36"/>
@@ -5630,7 +5672,7 @@
     <row r="69" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="C69" s="58" t="s">
@@ -5661,16 +5703,17 @@
         <v>6</v>
       </c>
       <c r="L69" s="38">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="M69" s="38">
         <v>80</v>
       </c>
-      <c r="M69" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N69" s="65">
+      <c r="N69" s="63">
         <v>0.13270000000000001</v>
       </c>
-      <c r="O69" s="65">
-        <f t="shared" si="1"/>
+      <c r="O69" s="63">
+        <f t="shared" si="4"/>
         <v>10.616000000000001</v>
       </c>
       <c r="P69" s="38"/>
@@ -5709,16 +5752,17 @@
         <v>3</v>
       </c>
       <c r="L70" s="36">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M70" s="36">
         <v>50</v>
       </c>
-      <c r="M70" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N70" s="63">
+      <c r="N70" s="62">
         <v>0.11330000000000001</v>
       </c>
-      <c r="O70" s="63">
-        <f t="shared" si="1"/>
+      <c r="O70" s="62">
+        <f t="shared" si="4"/>
         <v>5.6650000000000009</v>
       </c>
       <c r="P70" s="36"/>
@@ -5726,7 +5770,7 @@
     <row r="71" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="C71" s="58" t="s">
@@ -5757,16 +5801,17 @@
         <v>1</v>
       </c>
       <c r="L71" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M71" s="38">
         <v>20</v>
       </c>
-      <c r="M71" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N71" s="65">
+      <c r="N71" s="63">
         <v>0.12590000000000001</v>
       </c>
-      <c r="O71" s="65">
-        <f t="shared" si="1"/>
+      <c r="O71" s="63">
+        <f t="shared" si="4"/>
         <v>2.5180000000000002</v>
       </c>
       <c r="P71" s="38"/>
@@ -5805,16 +5850,17 @@
         <v>1</v>
       </c>
       <c r="L72" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M72" s="36">
         <v>20</v>
       </c>
-      <c r="M72" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N72" s="63">
+      <c r="N72" s="62">
         <v>0.12859999999999999</v>
       </c>
-      <c r="O72" s="63">
-        <f t="shared" si="1"/>
+      <c r="O72" s="62">
+        <f t="shared" si="4"/>
         <v>2.5720000000000001</v>
       </c>
       <c r="P72" s="36"/>
@@ -5822,7 +5868,7 @@
     <row r="73" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="C73" s="58" t="s">
@@ -5853,16 +5899,17 @@
         <v>1</v>
       </c>
       <c r="L73" s="38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M73" s="38">
         <v>100</v>
       </c>
-      <c r="M73" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N73" s="65">
+      <c r="N73" s="63">
         <v>0.1014</v>
       </c>
-      <c r="O73" s="65">
-        <f t="shared" si="1"/>
+      <c r="O73" s="63">
+        <f t="shared" si="4"/>
         <v>10.14</v>
       </c>
       <c r="P73" s="38"/>
@@ -5901,16 +5948,17 @@
         <v>1</v>
       </c>
       <c r="L74" s="36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M74" s="36">
         <v>100</v>
       </c>
-      <c r="M74" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N74" s="63">
+      <c r="N74" s="62">
         <v>0.10120000000000001</v>
       </c>
-      <c r="O74" s="63">
-        <f t="shared" si="1"/>
+      <c r="O74" s="62">
+        <f t="shared" si="4"/>
         <v>10.120000000000001</v>
       </c>
       <c r="P74" s="36"/>
@@ -5918,7 +5966,7 @@
     <row r="75" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="C75" s="58" t="s">
@@ -5949,16 +5997,17 @@
         <v>1</v>
       </c>
       <c r="L75" s="38">
+        <f t="shared" ref="L75:L119" si="5">K75*10</f>
+        <v>10</v>
+      </c>
+      <c r="M75" s="38">
         <v>100</v>
       </c>
-      <c r="M75" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N75" s="65">
+      <c r="N75" s="63">
         <v>0.10110000000000001</v>
       </c>
-      <c r="O75" s="65">
-        <f t="shared" ref="O75:O119" si="2">N75*L75</f>
+      <c r="O75" s="63">
+        <f t="shared" si="4"/>
         <v>10.110000000000001</v>
       </c>
       <c r="P75" s="38"/>
@@ -5997,16 +6046,17 @@
         <v>1</v>
       </c>
       <c r="L76" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M76" s="36">
         <v>20</v>
       </c>
-      <c r="M76" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N76" s="63">
+      <c r="N76" s="62">
         <v>0.12590000000000001</v>
       </c>
-      <c r="O76" s="63">
-        <f t="shared" si="2"/>
+      <c r="O76" s="62">
+        <f t="shared" si="4"/>
         <v>2.5180000000000002</v>
       </c>
       <c r="P76" s="36"/>
@@ -6014,7 +6064,7 @@
     <row r="77" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="C77" s="58" t="s">
@@ -6045,16 +6095,17 @@
         <v>6</v>
       </c>
       <c r="L77" s="38">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="M77" s="38">
         <v>100</v>
       </c>
-      <c r="M77" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N77" s="65">
+      <c r="N77" s="63">
         <v>0.1013</v>
       </c>
-      <c r="O77" s="65">
-        <f t="shared" si="2"/>
+      <c r="O77" s="63">
+        <f t="shared" si="4"/>
         <v>10.130000000000001</v>
       </c>
       <c r="P77" s="38"/>
@@ -6093,16 +6144,17 @@
         <v>10</v>
       </c>
       <c r="L78" s="36">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M78" s="36">
         <v>200</v>
       </c>
-      <c r="M78" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N78" s="63">
+      <c r="N78" s="62">
         <v>0.10100000000000001</v>
       </c>
-      <c r="O78" s="63">
-        <f t="shared" si="2"/>
+      <c r="O78" s="62">
+        <f t="shared" si="4"/>
         <v>20.200000000000003</v>
       </c>
       <c r="P78" s="36"/>
@@ -6110,7 +6162,7 @@
     <row r="79" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="C79" s="58" t="s">
@@ -6141,16 +6193,17 @@
         <v>1</v>
       </c>
       <c r="L79" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M79" s="38">
         <v>100</v>
       </c>
-      <c r="M79" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N79" s="65">
+      <c r="N79" s="63">
         <v>0.10310000000000001</v>
       </c>
-      <c r="O79" s="65">
-        <f t="shared" si="2"/>
+      <c r="O79" s="63">
+        <f t="shared" si="4"/>
         <v>10.31</v>
       </c>
       <c r="P79" s="38"/>
@@ -6189,16 +6242,17 @@
         <v>3</v>
       </c>
       <c r="L80" s="36">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="M80" s="36">
         <v>100</v>
       </c>
-      <c r="M80" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N80" s="63">
+      <c r="N80" s="62">
         <v>0.1009</v>
       </c>
-      <c r="O80" s="63">
-        <f t="shared" si="2"/>
+      <c r="O80" s="62">
+        <f t="shared" si="4"/>
         <v>10.09</v>
       </c>
       <c r="P80" s="36"/>
@@ -6206,7 +6260,7 @@
     <row r="81" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="C81" s="58" t="s">
@@ -6237,16 +6291,17 @@
         <v>1</v>
       </c>
       <c r="L81" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M81" s="38">
         <v>20</v>
       </c>
-      <c r="M81" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N81" s="65">
+      <c r="N81" s="63">
         <v>0.11940000000000001</v>
       </c>
-      <c r="O81" s="65">
-        <f t="shared" si="2"/>
+      <c r="O81" s="63">
+        <f t="shared" si="4"/>
         <v>2.3879999999999999</v>
       </c>
       <c r="P81" s="38"/>
@@ -6285,16 +6340,17 @@
         <v>1</v>
       </c>
       <c r="L82" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M82" s="36">
         <v>100</v>
       </c>
-      <c r="M82" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N82" s="63">
+      <c r="N82" s="62">
         <v>0.10200000000000001</v>
       </c>
-      <c r="O82" s="63">
-        <f t="shared" si="2"/>
+      <c r="O82" s="62">
+        <f t="shared" si="4"/>
         <v>10.200000000000001</v>
       </c>
       <c r="P82" s="36"/>
@@ -6302,7 +6358,7 @@
     <row r="83" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="C83" s="58" t="s">
@@ -6333,16 +6389,17 @@
         <v>10</v>
       </c>
       <c r="L83" s="38">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M83" s="38">
         <v>200</v>
       </c>
-      <c r="M83" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N83" s="65">
+      <c r="N83" s="63">
         <v>0.1008</v>
       </c>
-      <c r="O83" s="65">
-        <f t="shared" si="2"/>
+      <c r="O83" s="63">
+        <f t="shared" si="4"/>
         <v>20.16</v>
       </c>
       <c r="P83" s="38"/>
@@ -6381,16 +6438,17 @@
         <v>1</v>
       </c>
       <c r="L84" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M84" s="36">
         <v>50</v>
       </c>
-      <c r="M84" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N84" s="63">
+      <c r="N84" s="62">
         <v>0.10680000000000001</v>
       </c>
-      <c r="O84" s="63">
-        <f t="shared" si="2"/>
+      <c r="O84" s="62">
+        <f t="shared" si="4"/>
         <v>5.34</v>
       </c>
       <c r="P84" s="36"/>
@@ -6398,7 +6456,7 @@
     <row r="85" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="C85" s="58" t="s">
@@ -6429,16 +6487,17 @@
         <v>8</v>
       </c>
       <c r="L85" s="38">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="M85" s="38">
         <v>100</v>
       </c>
-      <c r="M85" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N85" s="65">
+      <c r="N85" s="63">
         <v>0.11430000000000001</v>
       </c>
-      <c r="O85" s="65">
-        <f t="shared" si="2"/>
+      <c r="O85" s="63">
+        <f t="shared" si="4"/>
         <v>11.430000000000001</v>
       </c>
       <c r="P85" s="38"/>
@@ -6477,16 +6536,17 @@
         <v>3</v>
       </c>
       <c r="L86" s="36">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="M86" s="36">
         <v>100</v>
       </c>
-      <c r="M86" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N86" s="63">
+      <c r="N86" s="62">
         <v>0.10300000000000001</v>
       </c>
-      <c r="O86" s="63">
-        <f t="shared" si="2"/>
+      <c r="O86" s="62">
+        <f t="shared" si="4"/>
         <v>10.3</v>
       </c>
       <c r="P86" s="36"/>
@@ -6494,7 +6554,7 @@
     <row r="87" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="C87" s="58" t="s">
@@ -6525,16 +6585,17 @@
         <v>2</v>
       </c>
       <c r="L87" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M87" s="38">
         <v>40</v>
       </c>
-      <c r="M87" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N87" s="65">
+      <c r="N87" s="63">
         <v>0.12570000000000001</v>
       </c>
-      <c r="O87" s="65">
-        <f t="shared" si="2"/>
+      <c r="O87" s="63">
+        <f t="shared" si="4"/>
         <v>5.0280000000000005</v>
       </c>
       <c r="P87" s="38"/>
@@ -6573,16 +6634,17 @@
         <v>1</v>
       </c>
       <c r="L88" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M88" s="36">
         <v>100</v>
       </c>
-      <c r="M88" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N88" s="63">
+      <c r="N88" s="62">
         <v>0.10400000000000001</v>
       </c>
-      <c r="O88" s="63">
-        <f t="shared" si="2"/>
+      <c r="O88" s="62">
+        <f t="shared" si="4"/>
         <v>10.4</v>
       </c>
       <c r="P88" s="36"/>
@@ -6590,7 +6652,7 @@
     <row r="89" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="C89" s="58" t="s">
@@ -6621,16 +6683,17 @@
         <v>3</v>
       </c>
       <c r="L89" s="38">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="M89" s="38">
         <v>100</v>
       </c>
-      <c r="M89" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N89" s="65">
+      <c r="N89" s="63">
         <v>0.10110000000000001</v>
       </c>
-      <c r="O89" s="65">
-        <f t="shared" si="2"/>
+      <c r="O89" s="63">
+        <f t="shared" si="4"/>
         <v>10.110000000000001</v>
       </c>
       <c r="P89" s="38"/>
@@ -6669,16 +6732,17 @@
         <v>2</v>
       </c>
       <c r="L90" s="36">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M90" s="36">
         <v>100</v>
       </c>
-      <c r="M90" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N90" s="63">
+      <c r="N90" s="62">
         <v>0.10110000000000001</v>
       </c>
-      <c r="O90" s="63">
-        <f t="shared" si="2"/>
+      <c r="O90" s="62">
+        <f t="shared" si="4"/>
         <v>10.110000000000001</v>
       </c>
       <c r="P90" s="36"/>
@@ -6686,7 +6750,7 @@
     <row r="91" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="C91" s="58" t="s">
@@ -6717,16 +6781,17 @@
         <v>1</v>
       </c>
       <c r="L91" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M91" s="38">
         <v>100</v>
       </c>
-      <c r="M91" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N91" s="65">
+      <c r="N91" s="63">
         <v>0.1013</v>
       </c>
-      <c r="O91" s="65">
-        <f t="shared" si="2"/>
+      <c r="O91" s="63">
+        <f t="shared" si="4"/>
         <v>10.130000000000001</v>
       </c>
       <c r="P91" s="38"/>
@@ -6765,16 +6830,17 @@
         <v>5</v>
       </c>
       <c r="L92" s="36">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="M92" s="36">
         <v>100</v>
       </c>
-      <c r="M92" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N92" s="63">
+      <c r="N92" s="62">
         <v>0.1014</v>
       </c>
-      <c r="O92" s="63">
-        <f t="shared" si="2"/>
+      <c r="O92" s="62">
+        <f t="shared" si="4"/>
         <v>10.14</v>
       </c>
       <c r="P92" s="36"/>
@@ -6782,7 +6848,7 @@
     <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="C93" s="58" t="s">
@@ -6813,16 +6879,17 @@
         <v>2</v>
       </c>
       <c r="L93" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M93" s="38">
         <v>100</v>
       </c>
-      <c r="M93" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N93" s="65">
+      <c r="N93" s="63">
         <v>0.1014</v>
       </c>
-      <c r="O93" s="65">
-        <f t="shared" si="2"/>
+      <c r="O93" s="63">
+        <f t="shared" si="4"/>
         <v>10.14</v>
       </c>
       <c r="P93" s="38"/>
@@ -6861,16 +6928,17 @@
         <v>2</v>
       </c>
       <c r="L94" s="36">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M94" s="36">
         <v>100</v>
       </c>
-      <c r="M94" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N94" s="63">
+      <c r="N94" s="62">
         <v>0.10120000000000001</v>
       </c>
-      <c r="O94" s="63">
-        <f t="shared" si="2"/>
+      <c r="O94" s="62">
+        <f t="shared" si="4"/>
         <v>10.120000000000001</v>
       </c>
       <c r="P94" s="36"/>
@@ -6878,7 +6946,7 @@
     <row r="95" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="C95" s="58" t="s">
@@ -6909,16 +6977,17 @@
         <v>4</v>
       </c>
       <c r="L95" s="38">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="M95" s="38">
         <v>45</v>
       </c>
-      <c r="M95" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N95" s="65">
+      <c r="N95" s="63">
         <v>0.1855</v>
       </c>
-      <c r="O95" s="65">
-        <f t="shared" si="2"/>
+      <c r="O95" s="63">
+        <f t="shared" si="4"/>
         <v>8.3475000000000001</v>
       </c>
       <c r="P95" s="38"/>
@@ -6957,16 +7026,17 @@
         <v>2</v>
       </c>
       <c r="L96" s="36">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M96" s="36">
         <v>50</v>
       </c>
-      <c r="M96" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N96" s="63">
+      <c r="N96" s="62">
         <v>0.10490000000000001</v>
       </c>
-      <c r="O96" s="63">
-        <f t="shared" si="2"/>
+      <c r="O96" s="62">
+        <f t="shared" si="4"/>
         <v>5.2450000000000001</v>
       </c>
       <c r="P96" s="36"/>
@@ -6974,7 +7044,7 @@
     <row r="97" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="C97" s="58" t="s">
@@ -7005,16 +7075,17 @@
         <v>2</v>
       </c>
       <c r="L97" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M97" s="38">
         <v>100</v>
       </c>
-      <c r="M97" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N97" s="65">
+      <c r="N97" s="63">
         <v>0.1014</v>
       </c>
-      <c r="O97" s="65">
-        <f t="shared" si="2"/>
+      <c r="O97" s="63">
+        <f t="shared" si="4"/>
         <v>10.14</v>
       </c>
       <c r="P97" s="38"/>
@@ -7053,16 +7124,17 @@
         <v>1</v>
       </c>
       <c r="L98" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M98" s="36">
         <v>20</v>
       </c>
-      <c r="M98" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N98" s="63">
+      <c r="N98" s="62">
         <v>0.1361</v>
       </c>
-      <c r="O98" s="63">
-        <f t="shared" si="2"/>
+      <c r="O98" s="62">
+        <f t="shared" si="4"/>
         <v>2.722</v>
       </c>
       <c r="P98" s="36"/>
@@ -7070,7 +7142,7 @@
     <row r="99" spans="1:16" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="C99" s="58" t="s">
@@ -7100,16 +7172,17 @@
       <c r="K99" s="39">
         <v>33</v>
       </c>
-      <c r="L99" s="38" t="s">
-        <v>480</v>
-      </c>
-      <c r="M99" s="64" t="s">
-        <v>480</v>
-      </c>
-      <c r="N99" s="65">
+      <c r="L99" s="38">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+      <c r="M99" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="N99" s="63">
         <v>0</v>
       </c>
-      <c r="O99" s="65" t="s">
+      <c r="O99" s="63" t="s">
         <v>480</v>
       </c>
       <c r="P99" s="38"/>
@@ -7148,16 +7221,17 @@
         <v>7</v>
       </c>
       <c r="L100" s="36">
+        <f t="shared" si="5"/>
+        <v>70</v>
+      </c>
+      <c r="M100" s="36">
         <v>80</v>
       </c>
-      <c r="M100" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N100" s="63">
+      <c r="N100" s="62">
         <v>0.1595</v>
       </c>
-      <c r="O100" s="63">
-        <f t="shared" si="2"/>
+      <c r="O100" s="62">
+        <f t="shared" ref="O100:O119" si="6">N100*M100</f>
         <v>12.76</v>
       </c>
       <c r="P100" s="36"/>
@@ -7165,7 +7239,7 @@
     <row r="101" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="C101" s="58" t="s">
@@ -7174,41 +7248,42 @@
       <c r="D101" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="E101" s="70" t="s">
+      <c r="E101" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="F101" s="71" t="s">
+      <c r="F101" s="69" t="s">
         <v>487</v>
       </c>
-      <c r="G101" s="70" t="s">
+      <c r="G101" s="68" t="s">
         <v>266</v>
       </c>
-      <c r="H101" s="71" t="s">
-        <v>480</v>
-      </c>
-      <c r="I101" s="71" t="s">
+      <c r="H101" s="69" t="s">
+        <v>480</v>
+      </c>
+      <c r="I101" s="69" t="s">
         <v>393</v>
       </c>
-      <c r="J101" s="71" t="s">
-        <v>480</v>
-      </c>
-      <c r="K101" s="70">
+      <c r="J101" s="69" t="s">
+        <v>480</v>
+      </c>
+      <c r="K101" s="68">
         <v>1</v>
       </c>
-      <c r="L101" s="71">
+      <c r="L101" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M101" s="69">
         <v>11</v>
       </c>
-      <c r="M101" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N101" s="65">
+      <c r="N101" s="63">
         <v>0.3</v>
       </c>
-      <c r="O101" s="72">
-        <f t="shared" si="2"/>
+      <c r="O101" s="70">
+        <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
-      <c r="P101" s="68"/>
+      <c r="P101" s="66"/>
     </row>
     <row r="102" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
@@ -7244,16 +7319,17 @@
         <v>1</v>
       </c>
       <c r="L102" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M102" s="36">
         <v>12</v>
       </c>
-      <c r="M102" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N102" s="63">
+      <c r="N102" s="62">
         <v>0.66289999999999993</v>
       </c>
-      <c r="O102" s="63">
-        <f t="shared" si="2"/>
+      <c r="O102" s="62">
+        <f t="shared" si="6"/>
         <v>7.9547999999999988</v>
       </c>
       <c r="P102" s="36"/>
@@ -7261,7 +7337,7 @@
     <row r="103" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="C103" s="58" t="s">
@@ -7292,16 +7368,17 @@
         <v>2</v>
       </c>
       <c r="L103" s="38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M103" s="38">
         <v>22</v>
       </c>
-      <c r="M103" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N103" s="65">
+      <c r="N103" s="63">
         <v>0.25480000000000003</v>
       </c>
-      <c r="O103" s="65">
-        <f t="shared" si="2"/>
+      <c r="O103" s="63">
+        <f t="shared" si="6"/>
         <v>5.6056000000000008</v>
       </c>
       <c r="P103" s="38"/>
@@ -7340,16 +7417,17 @@
         <v>1</v>
       </c>
       <c r="L104" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M104" s="36">
         <v>11</v>
       </c>
-      <c r="M104" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N104" s="63">
+      <c r="N104" s="62">
         <v>0.25559999999999999</v>
       </c>
-      <c r="O104" s="63">
-        <f t="shared" si="2"/>
+      <c r="O104" s="62">
+        <f t="shared" si="6"/>
         <v>2.8115999999999999</v>
       </c>
       <c r="P104" s="36"/>
@@ -7357,7 +7435,7 @@
     <row r="105" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="C105" s="58" t="s">
@@ -7388,16 +7466,17 @@
         <v>1</v>
       </c>
       <c r="L105" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M105" s="38">
         <v>12</v>
       </c>
-      <c r="M105" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N105" s="65">
+      <c r="N105" s="63">
         <v>0.29189999999999999</v>
       </c>
-      <c r="O105" s="65">
-        <f t="shared" si="2"/>
+      <c r="O105" s="63">
+        <f t="shared" si="6"/>
         <v>3.5027999999999997</v>
       </c>
       <c r="P105" s="38"/>
@@ -7436,16 +7515,17 @@
         <v>1</v>
       </c>
       <c r="L106" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M106" s="36">
         <v>15</v>
       </c>
-      <c r="M106" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N106" s="63">
+      <c r="N106" s="62">
         <v>0.23039999999999999</v>
       </c>
-      <c r="O106" s="63">
-        <f t="shared" si="2"/>
+      <c r="O106" s="62">
+        <f t="shared" si="6"/>
         <v>3.456</v>
       </c>
       <c r="P106" s="36"/>
@@ -7453,7 +7533,7 @@
     <row r="107" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="C107" s="58" t="s">
@@ -7484,16 +7564,17 @@
         <v>1</v>
       </c>
       <c r="L107" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M107" s="38">
         <v>12</v>
       </c>
-      <c r="M107" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N107" s="65">
+      <c r="N107" s="63">
         <v>0.41849999999999998</v>
       </c>
-      <c r="O107" s="65">
-        <f t="shared" si="2"/>
+      <c r="O107" s="63">
+        <f t="shared" si="6"/>
         <v>5.0220000000000002</v>
       </c>
       <c r="P107" s="38"/>
@@ -7532,16 +7613,17 @@
         <v>1</v>
       </c>
       <c r="L108" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M108" s="36">
         <v>11</v>
       </c>
-      <c r="M108" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N108" s="63">
+      <c r="N108" s="62">
         <v>2.06</v>
       </c>
-      <c r="O108" s="63">
-        <f t="shared" si="2"/>
+      <c r="O108" s="62">
+        <f t="shared" si="6"/>
         <v>22.66</v>
       </c>
       <c r="P108" s="36"/>
@@ -7549,7 +7631,7 @@
     <row r="109" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="C109" s="58" t="s">
@@ -7580,16 +7662,17 @@
         <v>1</v>
       </c>
       <c r="L109" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M109" s="38">
         <v>11</v>
       </c>
-      <c r="M109" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N109" s="65">
+      <c r="N109" s="63">
         <v>20.93</v>
       </c>
-      <c r="O109" s="65">
-        <f t="shared" si="2"/>
+      <c r="O109" s="63">
+        <f t="shared" si="6"/>
         <v>230.23</v>
       </c>
       <c r="P109" s="38"/>
@@ -7628,16 +7711,17 @@
         <v>2</v>
       </c>
       <c r="L110" s="36">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M110" s="36">
         <v>25</v>
       </c>
-      <c r="M110" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N110" s="63">
+      <c r="N110" s="62">
         <v>0.2409</v>
       </c>
-      <c r="O110" s="63">
-        <f t="shared" si="2"/>
+      <c r="O110" s="62">
+        <f t="shared" si="6"/>
         <v>6.0225</v>
       </c>
       <c r="P110" s="36"/>
@@ -7645,7 +7729,7 @@
     <row r="111" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="C111" s="58" t="s">
@@ -7676,16 +7760,17 @@
         <v>1</v>
       </c>
       <c r="L111" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M111" s="38">
         <v>11</v>
       </c>
-      <c r="M111" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N111" s="65">
+      <c r="N111" s="63">
         <v>0.96409999999999996</v>
       </c>
-      <c r="O111" s="65">
-        <f t="shared" si="2"/>
+      <c r="O111" s="63">
+        <f t="shared" si="6"/>
         <v>10.6051</v>
       </c>
       <c r="P111" s="38"/>
@@ -7724,16 +7809,17 @@
         <v>1</v>
       </c>
       <c r="L112" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M112" s="36">
         <v>11</v>
       </c>
-      <c r="M112" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N112" s="63">
+      <c r="N112" s="62">
         <v>6.3104999999999993</v>
       </c>
-      <c r="O112" s="63">
-        <f t="shared" si="2"/>
+      <c r="O112" s="62">
+        <f t="shared" si="6"/>
         <v>69.415499999999994</v>
       </c>
       <c r="P112" s="36"/>
@@ -7741,7 +7827,7 @@
     <row r="113" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="C113" s="58" t="s">
@@ -7772,16 +7858,17 @@
         <v>1</v>
       </c>
       <c r="L113" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M113" s="38">
         <v>11</v>
       </c>
-      <c r="M113" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N113" s="65">
+      <c r="N113" s="63">
         <v>14.936</v>
       </c>
-      <c r="O113" s="65">
-        <f t="shared" si="2"/>
+      <c r="O113" s="63">
+        <f t="shared" si="6"/>
         <v>164.29599999999999</v>
       </c>
       <c r="P113" s="38"/>
@@ -7820,16 +7907,17 @@
         <v>1</v>
       </c>
       <c r="L114" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M114" s="36">
         <v>11</v>
       </c>
-      <c r="M114" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N114" s="63">
+      <c r="N114" s="62">
         <v>13.7875</v>
       </c>
-      <c r="O114" s="63">
-        <f t="shared" si="2"/>
+      <c r="O114" s="62">
+        <f t="shared" si="6"/>
         <v>151.66249999999999</v>
       </c>
       <c r="P114" s="36"/>
@@ -7837,7 +7925,7 @@
     <row r="115" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="C115" s="58" t="s">
@@ -7868,16 +7956,17 @@
         <v>1</v>
       </c>
       <c r="L115" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M115" s="38">
         <v>11</v>
       </c>
-      <c r="M115" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N115" s="65">
+      <c r="N115" s="63">
         <v>17.600000000000001</v>
       </c>
-      <c r="O115" s="65">
-        <f t="shared" si="2"/>
+      <c r="O115" s="63">
+        <f t="shared" si="6"/>
         <v>193.60000000000002</v>
       </c>
       <c r="P115" s="38"/>
@@ -7916,16 +8005,17 @@
         <v>2</v>
       </c>
       <c r="L116" s="36">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="M116" s="36">
         <v>22</v>
       </c>
-      <c r="M116" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N116" s="63">
+      <c r="N116" s="62">
         <v>0.44950000000000001</v>
       </c>
-      <c r="O116" s="63">
-        <f t="shared" si="2"/>
+      <c r="O116" s="62">
+        <f t="shared" si="6"/>
         <v>9.8889999999999993</v>
       </c>
       <c r="P116" s="36"/>
@@ -7933,7 +8023,7 @@
     <row r="117" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="C117" s="58" t="s">
@@ -7964,16 +8054,17 @@
         <v>1</v>
       </c>
       <c r="L117" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M117" s="38">
         <v>15</v>
       </c>
-      <c r="M117" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N117" s="65">
+      <c r="N117" s="63">
         <v>0.1865</v>
       </c>
-      <c r="O117" s="65">
-        <f t="shared" si="2"/>
+      <c r="O117" s="63">
+        <f t="shared" si="6"/>
         <v>2.7974999999999999</v>
       </c>
       <c r="P117" s="38"/>
@@ -8012,16 +8103,17 @@
         <v>1</v>
       </c>
       <c r="L118" s="36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M118" s="36">
         <v>11</v>
       </c>
-      <c r="M118" s="62" t="s">
-        <v>514</v>
-      </c>
-      <c r="N118" s="63">
+      <c r="N118" s="62">
         <v>0.26180000000000003</v>
       </c>
-      <c r="O118" s="63">
-        <f t="shared" si="2"/>
+      <c r="O118" s="62">
+        <f t="shared" si="6"/>
         <v>2.8798000000000004</v>
       </c>
       <c r="P118" s="36"/>
@@ -8029,7 +8121,7 @@
     <row r="119" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="C119" s="58" t="s">
@@ -8060,16 +8152,17 @@
         <v>1</v>
       </c>
       <c r="L119" s="38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M119" s="38">
         <v>11</v>
       </c>
-      <c r="M119" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="N119" s="65">
+      <c r="N119" s="63">
         <v>0.34360000000000002</v>
       </c>
-      <c r="O119" s="65">
-        <f t="shared" si="2"/>
+      <c r="O119" s="63">
+        <f t="shared" si="6"/>
         <v>3.7796000000000003</v>
       </c>
       <c r="P119" s="38"/>
@@ -8086,12 +8179,12 @@
       <c r="I120" s="34"/>
       <c r="J120" s="35"/>
       <c r="K120" s="35"/>
-      <c r="L120" s="76" t="s">
-        <v>510</v>
-      </c>
-      <c r="M120" s="77"/>
-      <c r="N120" s="77"/>
-      <c r="O120" s="66">
+      <c r="L120" s="35"/>
+      <c r="M120" s="74" t="s">
+        <v>509</v>
+      </c>
+      <c r="N120" s="75"/>
+      <c r="O120" s="64">
         <f>SUM(O10:O119)</f>
         <v>1787.6428999999998</v>
       </c>
@@ -8109,12 +8202,12 @@
       <c r="I121" s="9"/>
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
-      <c r="L121" s="76" t="s">
-        <v>511</v>
-      </c>
-      <c r="M121" s="77"/>
-      <c r="N121" s="77"/>
-      <c r="O121" s="67">
+      <c r="L121" s="9"/>
+      <c r="M121" s="74" t="s">
+        <v>510</v>
+      </c>
+      <c r="N121" s="75"/>
+      <c r="O121" s="65">
         <f>O120/10</f>
         <v>178.76428999999999</v>
       </c>
@@ -8124,8 +8217,8 @@
   <mergeCells count="4">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="P3:P8"/>
-    <mergeCell ref="L120:N120"/>
-    <mergeCell ref="L121:N121"/>
+    <mergeCell ref="M120:N120"/>
+    <mergeCell ref="M121:N121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
